--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305425</v>
+        <v>120305213</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483637</v>
+        <v>483661</v>
       </c>
       <c r="R22" t="n">
-        <v>7019655</v>
+        <v>7019669</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305213</v>
+        <v>120305425</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483661</v>
+        <v>483637</v>
       </c>
       <c r="R23" t="n">
-        <v>7019669</v>
+        <v>7019655</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305213</v>
+        <v>120305425</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483661</v>
+        <v>483637</v>
       </c>
       <c r="R22" t="n">
-        <v>7019669</v>
+        <v>7019655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305425</v>
+        <v>120305213</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483637</v>
+        <v>483661</v>
       </c>
       <c r="R23" t="n">
-        <v>7019655</v>
+        <v>7019669</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120305415</v>
+        <v>120305432</v>
       </c>
       <c r="B2" t="n">
-        <v>74622</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483864</v>
+        <v>483629</v>
       </c>
       <c r="R2" t="n">
-        <v>7019545</v>
+        <v>7019655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305439</v>
+        <v>120305320</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483782</v>
+        <v>483836</v>
       </c>
       <c r="R3" t="n">
-        <v>7019560</v>
+        <v>7019556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>120305462</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305214</v>
+        <v>120305355</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1031,24 +1031,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483756</v>
+        <v>483741</v>
       </c>
       <c r="R5" t="n">
-        <v>7019560</v>
+        <v>7019614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305416</v>
+        <v>120305296</v>
       </c>
       <c r="B6" t="n">
-        <v>74622</v>
+        <v>96885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483989</v>
+        <v>483979</v>
       </c>
       <c r="R6" t="n">
-        <v>7019538</v>
+        <v>7019514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120305320</v>
+        <v>120305196</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483836</v>
+        <v>483658</v>
       </c>
       <c r="R7" t="n">
-        <v>7019556</v>
+        <v>7019677</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,17 +1304,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305464</v>
+        <v>120305295</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>96885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1363,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483889</v>
+        <v>483819</v>
       </c>
       <c r="R8" t="n">
-        <v>7019544</v>
+        <v>7019570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305195</v>
+        <v>120305433</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1469,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483673</v>
+        <v>483702</v>
       </c>
       <c r="R9" t="n">
-        <v>7019675</v>
+        <v>7019609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305297</v>
+        <v>120305416</v>
       </c>
       <c r="B10" t="n">
-        <v>96862</v>
+        <v>74638</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1575,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484003</v>
+        <v>483989</v>
       </c>
       <c r="R10" t="n">
-        <v>7019580</v>
+        <v>7019538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305278</v>
+        <v>120305234</v>
       </c>
       <c r="B11" t="n">
-        <v>96862</v>
+        <v>90527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,16 +1667,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483813</v>
+        <v>483609</v>
       </c>
       <c r="R11" t="n">
-        <v>7019540</v>
+        <v>7019727</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,12 +1714,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lurigt växtsätt inuti hålighet på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1736,17 +1737,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305353</v>
+        <v>120305439</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1756,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483754</v>
+        <v>483782</v>
       </c>
       <c r="R12" t="n">
-        <v>7019590</v>
+        <v>7019560</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305295</v>
+        <v>120305195</v>
       </c>
       <c r="B13" t="n">
-        <v>96862</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1893,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483819</v>
+        <v>483673</v>
       </c>
       <c r="R13" t="n">
-        <v>7019570</v>
+        <v>7019675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,17 +1949,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305432</v>
+        <v>120305214</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1993,16 +1994,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483629</v>
+        <v>483756</v>
       </c>
       <c r="R14" t="n">
-        <v>7019655</v>
+        <v>7019560</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,17 +2063,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305354</v>
+        <v>120305464</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2073,25 +2082,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2105,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483639</v>
+        <v>483889</v>
       </c>
       <c r="R15" t="n">
-        <v>7019659</v>
+        <v>7019544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305171</v>
+        <v>120305415</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>74638</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,25 +2188,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2211,10 +2220,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483590</v>
+        <v>483864</v>
       </c>
       <c r="R16" t="n">
-        <v>7019723</v>
+        <v>7019545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,10 +2282,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305234</v>
+        <v>120305353</v>
       </c>
       <c r="B17" t="n">
-        <v>90509</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,25 +2294,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2311,19 +2320,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483609</v>
+        <v>483754</v>
       </c>
       <c r="R17" t="n">
-        <v>7019727</v>
+        <v>7019590</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,18 +2364,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Lurigt växtsätt inuti hålighet på gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120305355</v>
+        <v>120305213</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2400,25 +2400,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483741</v>
+        <v>483661</v>
       </c>
       <c r="R18" t="n">
-        <v>7019614</v>
+        <v>7019669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,17 +2487,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305196</v>
+        <v>120305215</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2532,16 +2532,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483658</v>
+        <v>483868</v>
       </c>
       <c r="R19" t="n">
-        <v>7019677</v>
+        <v>7019544</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,17 +2601,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305215</v>
+        <v>120305278</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>96885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,25 +2620,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2638,24 +2646,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483868</v>
+        <v>483813</v>
       </c>
       <c r="R20" t="n">
-        <v>7019544</v>
+        <v>7019540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305296</v>
+        <v>120305172</v>
       </c>
       <c r="B21" t="n">
-        <v>96862</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2726,25 +2726,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483979</v>
+        <v>483662</v>
       </c>
       <c r="R21" t="n">
-        <v>7019514</v>
+        <v>7019676</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305425</v>
+        <v>120305404</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483637</v>
+        <v>483788</v>
       </c>
       <c r="R22" t="n">
-        <v>7019655</v>
+        <v>7019601</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305213</v>
+        <v>120305463</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483661</v>
+        <v>483849</v>
       </c>
       <c r="R23" t="n">
-        <v>7019669</v>
+        <v>7019545</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120305404</v>
+        <v>120305171</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483788</v>
+        <v>483590</v>
       </c>
       <c r="R24" t="n">
-        <v>7019601</v>
+        <v>7019723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305172</v>
+        <v>120305244</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>79527</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483662</v>
+        <v>483828</v>
       </c>
       <c r="R25" t="n">
-        <v>7019676</v>
+        <v>7019588</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305433</v>
+        <v>120305297</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483702</v>
+        <v>484003</v>
       </c>
       <c r="R26" t="n">
-        <v>7019609</v>
+        <v>7019580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305463</v>
+        <v>120305354</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3362,25 +3362,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483849</v>
+        <v>483639</v>
       </c>
       <c r="R27" t="n">
-        <v>7019545</v>
+        <v>7019659</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305244</v>
+        <v>120305425</v>
       </c>
       <c r="B28" t="n">
-        <v>79511</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483828</v>
+        <v>483637</v>
       </c>
       <c r="R28" t="n">
-        <v>7019588</v>
+        <v>7019655</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305195</v>
+        <v>120305214</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1888,16 +1888,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483673</v>
+        <v>483756</v>
       </c>
       <c r="R13" t="n">
-        <v>7019675</v>
+        <v>7019560</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305214</v>
+        <v>120305195</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1994,24 +2002,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483756</v>
+        <v>483673</v>
       </c>
       <c r="R14" t="n">
-        <v>7019560</v>
+        <v>7019675</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305215</v>
+        <v>120305278</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2506,25 +2506,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2532,24 +2532,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483868</v>
+        <v>483813</v>
       </c>
       <c r="R19" t="n">
-        <v>7019544</v>
+        <v>7019540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,17 +2593,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305278</v>
+        <v>120305215</v>
       </c>
       <c r="B20" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,25 +2612,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2646,16 +2638,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483813</v>
+        <v>483868</v>
       </c>
       <c r="R20" t="n">
-        <v>7019540</v>
+        <v>7019544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3560,6 +3560,530 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120382607</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Indalsälven, Indalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>483473</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7019629</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120382563</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Indalsälven, Indalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>483510</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7019662</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120383857</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vågen, Vågen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>483696</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7019783</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120382600</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Indalsälven, Indalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>483535</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7019649</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120383186</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Indalsälven, Indalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>483495</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7019685</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120305432</v>
+        <v>120305462</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483629</v>
+        <v>483700</v>
       </c>
       <c r="R2" t="n">
-        <v>7019655</v>
+        <v>7019608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305320</v>
+        <v>120305415</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>74638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483836</v>
+        <v>483864</v>
       </c>
       <c r="R3" t="n">
-        <v>7019556</v>
+        <v>7019545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305462</v>
+        <v>120305196</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483700</v>
+        <v>483658</v>
       </c>
       <c r="R4" t="n">
-        <v>7019608</v>
+        <v>7019677</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,17 +986,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305355</v>
+        <v>120305463</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483741</v>
+        <v>483849</v>
       </c>
       <c r="R5" t="n">
-        <v>7019614</v>
+        <v>7019545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305296</v>
+        <v>120305297</v>
       </c>
       <c r="B6" t="n">
         <v>96885</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483979</v>
+        <v>484003</v>
       </c>
       <c r="R6" t="n">
-        <v>7019514</v>
+        <v>7019580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120305196</v>
+        <v>120305464</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483658</v>
+        <v>483889</v>
       </c>
       <c r="R7" t="n">
-        <v>7019677</v>
+        <v>7019544</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305295</v>
+        <v>120305214</v>
       </c>
       <c r="B8" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1349,16 +1349,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483819</v>
+        <v>483756</v>
       </c>
       <c r="R8" t="n">
-        <v>7019570</v>
+        <v>7019560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,17 +1418,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305433</v>
+        <v>120305355</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1437,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483702</v>
+        <v>483741</v>
       </c>
       <c r="R9" t="n">
-        <v>7019609</v>
+        <v>7019614</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305416</v>
+        <v>120305425</v>
       </c>
       <c r="B10" t="n">
-        <v>74638</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1543,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483989</v>
+        <v>483637</v>
       </c>
       <c r="R10" t="n">
-        <v>7019538</v>
+        <v>7019655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305234</v>
+        <v>120305295</v>
       </c>
       <c r="B11" t="n">
-        <v>90527</v>
+        <v>96885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1649,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1667,19 +1675,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483609</v>
+        <v>483819</v>
       </c>
       <c r="R11" t="n">
-        <v>7019727</v>
+        <v>7019570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,18 +1719,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lurigt växtsätt inuti hålighet på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1737,17 +1736,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305439</v>
+        <v>120305320</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1788,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483782</v>
+        <v>483836</v>
       </c>
       <c r="R12" t="n">
-        <v>7019560</v>
+        <v>7019556</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305214</v>
+        <v>120305195</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1865,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1888,24 +1887,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483756</v>
+        <v>483673</v>
       </c>
       <c r="R13" t="n">
-        <v>7019560</v>
+        <v>7019675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305195</v>
+        <v>120305439</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2008,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483673</v>
+        <v>483782</v>
       </c>
       <c r="R14" t="n">
-        <v>7019675</v>
+        <v>7019560</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,17 +2054,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305464</v>
+        <v>120305433</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2114,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483889</v>
+        <v>483702</v>
       </c>
       <c r="R15" t="n">
-        <v>7019544</v>
+        <v>7019609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305415</v>
+        <v>120305296</v>
       </c>
       <c r="B16" t="n">
-        <v>74638</v>
+        <v>96885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,21 +2183,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2220,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483864</v>
+        <v>483979</v>
       </c>
       <c r="R16" t="n">
-        <v>7019545</v>
+        <v>7019514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305353</v>
+        <v>120305172</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,25 +2285,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2326,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483754</v>
+        <v>483662</v>
       </c>
       <c r="R17" t="n">
-        <v>7019590</v>
+        <v>7019676</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120305213</v>
+        <v>120305432</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,21 +2395,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2432,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483661</v>
+        <v>483629</v>
       </c>
       <c r="R18" t="n">
-        <v>7019669</v>
+        <v>7019655</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,17 +2478,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305278</v>
+        <v>120305213</v>
       </c>
       <c r="B19" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2506,25 +2497,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2538,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483813</v>
+        <v>483661</v>
       </c>
       <c r="R19" t="n">
-        <v>7019540</v>
+        <v>7019669</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,17 +2584,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305215</v>
+        <v>120305354</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,25 +2603,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2638,24 +2629,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483868</v>
+        <v>483639</v>
       </c>
       <c r="R20" t="n">
-        <v>7019544</v>
+        <v>7019659</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,17 +2690,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305172</v>
+        <v>120305234</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2713,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2752,16 +2735,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483662</v>
+        <v>483609</v>
       </c>
       <c r="R21" t="n">
-        <v>7019676</v>
+        <v>7019727</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2796,12 +2782,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Lurigt växtsätt inuti hålighet på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2813,17 +2805,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305404</v>
+        <v>120305171</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2824,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2864,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483788</v>
+        <v>483590</v>
       </c>
       <c r="R22" t="n">
-        <v>7019601</v>
+        <v>7019723</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305463</v>
+        <v>120305404</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,25 +2930,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2970,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483849</v>
+        <v>483788</v>
       </c>
       <c r="R23" t="n">
-        <v>7019545</v>
+        <v>7019601</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120305171</v>
+        <v>120305416</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>74638</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,25 +3036,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3076,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483590</v>
+        <v>483989</v>
       </c>
       <c r="R24" t="n">
-        <v>7019723</v>
+        <v>7019538</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305244</v>
+        <v>120305278</v>
       </c>
       <c r="B25" t="n">
-        <v>79527</v>
+        <v>96885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,21 +3146,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3182,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483828</v>
+        <v>483813</v>
       </c>
       <c r="R25" t="n">
-        <v>7019588</v>
+        <v>7019540</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,17 +3229,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305297</v>
+        <v>120305353</v>
       </c>
       <c r="B26" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3248,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3288,10 +3280,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484003</v>
+        <v>483754</v>
       </c>
       <c r="R26" t="n">
-        <v>7019580</v>
+        <v>7019590</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3342,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305354</v>
+        <v>120305215</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3362,25 +3354,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3388,16 +3380,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483639</v>
+        <v>483868</v>
       </c>
       <c r="R27" t="n">
-        <v>7019659</v>
+        <v>7019544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305425</v>
+        <v>120305244</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>79527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483637</v>
+        <v>483828</v>
       </c>
       <c r="R28" t="n">
-        <v>7019655</v>
+        <v>7019588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3555,17 +3555,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120382607</v>
+        <v>120383186</v>
       </c>
       <c r="B29" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,34 +3578,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483473</v>
+        <v>483495</v>
       </c>
       <c r="R29" t="n">
-        <v>7019629</v>
+        <v>7019685</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3970,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120383186</v>
+        <v>120382607</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3986,48 +4000,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483495</v>
+        <v>483473</v>
       </c>
       <c r="R33" t="n">
-        <v>7019685</v>
+        <v>7019629</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,6 +4083,2098 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120408127</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>483461</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7019658</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120408138</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>483468</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7019617</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120408141</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>483464</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7019618</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120408133</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>484009</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7019588</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120408134</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>484009</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7019590</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120408117</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>483561</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7019762</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120408128</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>483452</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7019647</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120408143</v>
+      </c>
+      <c r="B41" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>483743</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7019735</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120408123</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>483474</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7019669</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120408122</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>483606</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7019790</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120408131</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>483548</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7019602</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120408121</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>483627</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7019822</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120408125</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>483456</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7019660</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120408124</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>483470</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7019656</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120408144</v>
+      </c>
+      <c r="B48" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>483550</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7019749</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120408135</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>483713</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7019760</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120408132</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>483589</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7019600</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120408118</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>483476</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7019660</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>gammalt bohål</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120408116</v>
+      </c>
+      <c r="B52" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>483550</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7019749</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120408137</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>483624</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7019813</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3342,10 +3342,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305215</v>
+        <v>120305244</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3354,25 +3354,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3380,24 +3380,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483868</v>
+        <v>483828</v>
       </c>
       <c r="R27" t="n">
-        <v>7019544</v>
+        <v>7019588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3448,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305244</v>
+        <v>120305215</v>
       </c>
       <c r="B28" t="n">
-        <v>79527</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3468,25 +3460,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3494,16 +3486,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483828</v>
+        <v>483868</v>
       </c>
       <c r="R28" t="n">
-        <v>7019588</v>
+        <v>7019544</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6176,6 +6176,1808 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120420835</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>483638</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7019659</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120420832</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>483500</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7019677</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120420849</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>483572</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7019741</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120420872</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87409</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>483619</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7019709</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120420887</v>
+      </c>
+      <c r="B58" t="n">
+        <v>87423</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>483979</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7019620</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120420840</v>
+      </c>
+      <c r="B59" t="n">
+        <v>74638</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>483762</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7019692</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120420831</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>483607</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7019631</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120420833</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>483556</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7019737</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120420877</v>
+      </c>
+      <c r="B62" t="n">
+        <v>95478</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>53</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>483497</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7019675</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120420878</v>
+      </c>
+      <c r="B63" t="n">
+        <v>95478</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>53</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>483767</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7019702</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120420838</v>
+      </c>
+      <c r="B64" t="n">
+        <v>74646</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>308</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>483758</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7019694</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120420836</v>
+      </c>
+      <c r="B65" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>483663</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7019709</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120420837</v>
+      </c>
+      <c r="B66" t="n">
+        <v>74646</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>308</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>483750</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7019734</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120420830</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>483954</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7019556</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120420844</v>
+      </c>
+      <c r="B68" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>483852</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7019773</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120420883</v>
+      </c>
+      <c r="B69" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>483664</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7019708</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120420834</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>483657</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7019712</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120305462</v>
+        <v>120305214</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483700</v>
+        <v>483756</v>
       </c>
       <c r="R2" t="n">
-        <v>7019608</v>
+        <v>7019560</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305415</v>
+        <v>120305171</v>
       </c>
       <c r="B3" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483864</v>
+        <v>483590</v>
       </c>
       <c r="R3" t="n">
-        <v>7019545</v>
+        <v>7019723</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305196</v>
+        <v>120305355</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483658</v>
+        <v>483741</v>
       </c>
       <c r="R4" t="n">
-        <v>7019677</v>
+        <v>7019614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,17 +994,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305463</v>
+        <v>120305296</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483849</v>
+        <v>483979</v>
       </c>
       <c r="R5" t="n">
-        <v>7019545</v>
+        <v>7019514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305297</v>
+        <v>120305172</v>
       </c>
       <c r="B6" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1119,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484003</v>
+        <v>483662</v>
       </c>
       <c r="R6" t="n">
-        <v>7019580</v>
+        <v>7019676</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120305464</v>
+        <v>120305463</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1249,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483889</v>
+        <v>483849</v>
       </c>
       <c r="R7" t="n">
-        <v>7019544</v>
+        <v>7019545</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305214</v>
+        <v>120305297</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1331,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1349,24 +1357,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483756</v>
+        <v>484003</v>
       </c>
       <c r="R8" t="n">
-        <v>7019560</v>
+        <v>7019580</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305355</v>
+        <v>120305433</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,25 +1437,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483741</v>
+        <v>483702</v>
       </c>
       <c r="R9" t="n">
-        <v>7019614</v>
+        <v>7019609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305425</v>
+        <v>120305432</v>
       </c>
       <c r="B10" t="n">
         <v>90598</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483637</v>
+        <v>483629</v>
       </c>
       <c r="R10" t="n">
         <v>7019655</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305295</v>
+        <v>120305416</v>
       </c>
       <c r="B11" t="n">
-        <v>96885</v>
+        <v>74638</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483819</v>
+        <v>483989</v>
       </c>
       <c r="R11" t="n">
-        <v>7019570</v>
+        <v>7019538</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305320</v>
+        <v>120305425</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483836</v>
+        <v>483637</v>
       </c>
       <c r="R12" t="n">
-        <v>7019556</v>
+        <v>7019655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305195</v>
+        <v>120305320</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483673</v>
+        <v>483836</v>
       </c>
       <c r="R13" t="n">
-        <v>7019675</v>
+        <v>7019556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,17 +1948,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305439</v>
+        <v>120305244</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,25 +1967,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483782</v>
+        <v>483828</v>
       </c>
       <c r="R14" t="n">
-        <v>7019560</v>
+        <v>7019588</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305433</v>
+        <v>120305354</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2073,25 +2073,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483702</v>
+        <v>483639</v>
       </c>
       <c r="R15" t="n">
-        <v>7019609</v>
+        <v>7019659</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305296</v>
+        <v>120305278</v>
       </c>
       <c r="B16" t="n">
         <v>96885</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483979</v>
+        <v>483813</v>
       </c>
       <c r="R16" t="n">
-        <v>7019514</v>
+        <v>7019540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305172</v>
+        <v>120305439</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,21 +2289,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483662</v>
+        <v>483782</v>
       </c>
       <c r="R17" t="n">
-        <v>7019676</v>
+        <v>7019560</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120305432</v>
+        <v>120305464</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483629</v>
+        <v>483889</v>
       </c>
       <c r="R18" t="n">
-        <v>7019655</v>
+        <v>7019544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305213</v>
+        <v>120305404</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,25 +2497,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483661</v>
+        <v>483788</v>
       </c>
       <c r="R19" t="n">
-        <v>7019669</v>
+        <v>7019601</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,14 +2584,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305354</v>
+        <v>120305353</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483639</v>
+        <v>483754</v>
       </c>
       <c r="R20" t="n">
-        <v>7019659</v>
+        <v>7019590</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305234</v>
+        <v>120305295</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>96885</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,25 +2709,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2735,19 +2735,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483609</v>
+        <v>483819</v>
       </c>
       <c r="R21" t="n">
-        <v>7019727</v>
+        <v>7019570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2782,18 +2779,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Lurigt växtsätt inuti hålighet på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,17 +2796,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305171</v>
+        <v>120305215</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2828,21 +2819,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2850,16 +2841,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483590</v>
+        <v>483868</v>
       </c>
       <c r="R22" t="n">
-        <v>7019723</v>
+        <v>7019544</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305404</v>
+        <v>120305234</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2930,25 +2929,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2956,16 +2955,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483788</v>
+        <v>483609</v>
       </c>
       <c r="R23" t="n">
-        <v>7019601</v>
+        <v>7019727</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,12 +3002,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lurigt växtsätt inuti hålighet på gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3024,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120305416</v>
+        <v>120305196</v>
       </c>
       <c r="B24" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3036,25 +3044,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3068,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483989</v>
+        <v>483658</v>
       </c>
       <c r="R24" t="n">
-        <v>7019538</v>
+        <v>7019677</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305278</v>
+        <v>120305195</v>
       </c>
       <c r="B25" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,25 +3150,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3174,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483813</v>
+        <v>483673</v>
       </c>
       <c r="R25" t="n">
-        <v>7019540</v>
+        <v>7019675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305353</v>
+        <v>120305213</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3248,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3280,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483754</v>
+        <v>483661</v>
       </c>
       <c r="R26" t="n">
-        <v>7019590</v>
+        <v>7019669</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3342,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305244</v>
+        <v>120305462</v>
       </c>
       <c r="B27" t="n">
-        <v>79527</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3354,25 +3362,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3386,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483828</v>
+        <v>483700</v>
       </c>
       <c r="R27" t="n">
-        <v>7019588</v>
+        <v>7019608</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,17 +3449,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305215</v>
+        <v>120305415</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>74638</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3460,25 +3468,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3486,24 +3494,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483868</v>
+        <v>483864</v>
       </c>
       <c r="R28" t="n">
-        <v>7019544</v>
+        <v>7019545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3555,17 +3555,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120383186</v>
+        <v>120383857</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,48 +3578,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Indalsälven, Indalsälven, Jmt</t>
+          <t>Vågen, Vågen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483495</v>
+        <v>483696</v>
       </c>
       <c r="R29" t="n">
-        <v>7019685</v>
+        <v>7019783</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3780,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120383857</v>
+        <v>120383186</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3796,34 +3782,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vågen, Vågen, Jmt</t>
+          <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483696</v>
+        <v>483495</v>
       </c>
       <c r="R31" t="n">
-        <v>7019783</v>
+        <v>7019685</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120408127</v>
+        <v>120408134</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483461</v>
+        <v>484009</v>
       </c>
       <c r="R34" t="n">
-        <v>7019658</v>
+        <v>7019590</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4162,11 +4162,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4193,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120408138</v>
+        <v>120408141</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>90576</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4209,21 +4204,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4233,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483468</v>
+        <v>483464</v>
       </c>
       <c r="R35" t="n">
-        <v>7019617</v>
+        <v>7019618</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120408141</v>
+        <v>120408135</v>
       </c>
       <c r="B36" t="n">
-        <v>90576</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4311,21 +4306,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483464</v>
+        <v>483713</v>
       </c>
       <c r="R36" t="n">
-        <v>7019618</v>
+        <v>7019760</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4397,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120408133</v>
+        <v>120408128</v>
       </c>
       <c r="B37" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4413,21 +4408,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4437,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>484009</v>
+        <v>483452</v>
       </c>
       <c r="R37" t="n">
-        <v>7019588</v>
+        <v>7019647</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4473,6 +4468,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4499,7 +4499,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120408134</v>
+        <v>120408138</v>
       </c>
       <c r="B38" t="n">
         <v>79623</v>
@@ -4539,10 +4539,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>484009</v>
+        <v>483468</v>
       </c>
       <c r="R38" t="n">
-        <v>7019590</v>
+        <v>7019617</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4601,10 +4601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120408117</v>
+        <v>120408123</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4617,21 +4617,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483561</v>
+        <v>483474</v>
       </c>
       <c r="R39" t="n">
-        <v>7019762</v>
+        <v>7019669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,6 +4677,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4703,7 +4708,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120408128</v>
+        <v>120408125</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4743,10 +4748,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483452</v>
+        <v>483456</v>
       </c>
       <c r="R40" t="n">
-        <v>7019647</v>
+        <v>7019660</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4810,7 +4815,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120408143</v>
+        <v>120408144</v>
       </c>
       <c r="B41" t="n">
         <v>82321</v>
@@ -4850,10 +4855,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483743</v>
+        <v>483550</v>
       </c>
       <c r="R41" t="n">
-        <v>7019735</v>
+        <v>7019749</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,7 +4918,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120408123</v>
+        <v>120408127</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4953,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483474</v>
+        <v>483461</v>
       </c>
       <c r="R42" t="n">
-        <v>7019669</v>
+        <v>7019658</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4998,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5020,10 +5025,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120408122</v>
+        <v>120408133</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5036,21 +5041,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5060,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483606</v>
+        <v>484009</v>
       </c>
       <c r="R43" t="n">
-        <v>7019790</v>
+        <v>7019588</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5096,11 +5101,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5127,7 +5127,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120408131</v>
+        <v>120408121</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483548</v>
+        <v>483627</v>
       </c>
       <c r="R44" t="n">
-        <v>7019602</v>
+        <v>7019822</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120408121</v>
+        <v>120408131</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483627</v>
+        <v>483548</v>
       </c>
       <c r="R45" t="n">
-        <v>7019822</v>
+        <v>7019602</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120408125</v>
+        <v>120408124</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483456</v>
+        <v>483470</v>
       </c>
       <c r="R46" t="n">
-        <v>7019660</v>
+        <v>7019656</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5448,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120408124</v>
+        <v>120408122</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483470</v>
+        <v>483606</v>
       </c>
       <c r="R47" t="n">
-        <v>7019656</v>
+        <v>7019790</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120408144</v>
+        <v>120408116</v>
       </c>
       <c r="B48" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5639,7 +5639,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5658,10 +5657,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120408135</v>
+        <v>120408117</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5674,21 +5673,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5698,10 +5697,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483713</v>
+        <v>483561</v>
       </c>
       <c r="R49" t="n">
-        <v>7019760</v>
+        <v>7019762</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5760,10 +5759,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120408132</v>
+        <v>120408137</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5776,21 +5775,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5800,10 +5799,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483589</v>
+        <v>483624</v>
       </c>
       <c r="R50" t="n">
-        <v>7019600</v>
+        <v>7019813</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5836,11 +5835,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5867,10 +5861,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120408118</v>
+        <v>120408143</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5883,21 +5877,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5907,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483476</v>
+        <v>483743</v>
       </c>
       <c r="R51" t="n">
-        <v>7019660</v>
+        <v>7019735</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5945,17 +5939,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>gammalt bohål</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5974,10 +5964,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120408116</v>
+        <v>120408118</v>
       </c>
       <c r="B52" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5990,21 +5980,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6004,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483550</v>
+        <v>483476</v>
       </c>
       <c r="R52" t="n">
-        <v>7019749</v>
+        <v>7019660</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6050,6 +6040,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6076,10 +6071,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120408137</v>
+        <v>120408132</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6092,21 +6087,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483624</v>
+        <v>483589</v>
       </c>
       <c r="R53" t="n">
-        <v>7019813</v>
+        <v>7019600</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6152,6 +6147,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,10 +6178,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120420835</v>
+        <v>120420872</v>
       </c>
       <c r="B54" t="n">
-        <v>90598</v>
+        <v>87409</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>4405</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483638</v>
+        <v>483619</v>
       </c>
       <c r="R54" t="n">
-        <v>7019659</v>
+        <v>7019709</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120420832</v>
+        <v>120420838</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483500</v>
+        <v>483758</v>
       </c>
       <c r="R55" t="n">
-        <v>7019677</v>
+        <v>7019694</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120420849</v>
+        <v>120420835</v>
       </c>
       <c r="B56" t="n">
-        <v>79652</v>
+        <v>90598</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,25 +6402,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483572</v>
+        <v>483638</v>
       </c>
       <c r="R56" t="n">
-        <v>7019741</v>
+        <v>7019659</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6496,10 +6496,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120420872</v>
+        <v>120420883</v>
       </c>
       <c r="B57" t="n">
-        <v>87409</v>
+        <v>90576</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6508,25 +6508,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4405</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483619</v>
+        <v>483664</v>
       </c>
       <c r="R57" t="n">
-        <v>7019709</v>
+        <v>7019708</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6602,10 +6602,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120420887</v>
+        <v>120420834</v>
       </c>
       <c r="B58" t="n">
-        <v>87423</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6618,21 +6618,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483979</v>
+        <v>483657</v>
       </c>
       <c r="R58" t="n">
-        <v>7019620</v>
+        <v>7019712</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6708,10 +6708,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120420840</v>
+        <v>120420877</v>
       </c>
       <c r="B59" t="n">
-        <v>74638</v>
+        <v>95478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6720,25 +6720,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483762</v>
+        <v>483497</v>
       </c>
       <c r="R59" t="n">
-        <v>7019692</v>
+        <v>7019675</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120420831</v>
+        <v>120420832</v>
       </c>
       <c r="B60" t="n">
         <v>78542</v>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483607</v>
+        <v>483500</v>
       </c>
       <c r="R60" t="n">
-        <v>7019631</v>
+        <v>7019677</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120420833</v>
+        <v>120420836</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483556</v>
+        <v>483663</v>
       </c>
       <c r="R61" t="n">
-        <v>7019737</v>
+        <v>7019709</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120420877</v>
+        <v>120420849</v>
       </c>
       <c r="B62" t="n">
-        <v>95478</v>
+        <v>79652</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7038,25 +7038,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483497</v>
+        <v>483572</v>
       </c>
       <c r="R62" t="n">
-        <v>7019675</v>
+        <v>7019741</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120420838</v>
+        <v>120420887</v>
       </c>
       <c r="B64" t="n">
-        <v>74646</v>
+        <v>87423</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>308</v>
+        <v>4412</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483758</v>
+        <v>483979</v>
       </c>
       <c r="R64" t="n">
-        <v>7019694</v>
+        <v>7019620</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120420836</v>
+        <v>120420837</v>
       </c>
       <c r="B65" t="n">
-        <v>90598</v>
+        <v>74646</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483663</v>
+        <v>483750</v>
       </c>
       <c r="R65" t="n">
-        <v>7019709</v>
+        <v>7019734</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7450,10 +7450,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120420837</v>
+        <v>120420840</v>
       </c>
       <c r="B66" t="n">
-        <v>74646</v>
+        <v>74638</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7462,25 +7462,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483750</v>
+        <v>483762</v>
       </c>
       <c r="R66" t="n">
-        <v>7019734</v>
+        <v>7019692</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7556,10 +7556,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120420830</v>
+        <v>120420844</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7568,25 +7568,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483954</v>
+        <v>483852</v>
       </c>
       <c r="R67" t="n">
-        <v>7019556</v>
+        <v>7019773</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120420844</v>
+        <v>120420831</v>
       </c>
       <c r="B68" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7674,25 +7674,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483852</v>
+        <v>483607</v>
       </c>
       <c r="R68" t="n">
-        <v>7019773</v>
+        <v>7019631</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7768,10 +7768,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120420883</v>
+        <v>120420830</v>
       </c>
       <c r="B69" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7784,21 +7784,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483664</v>
+        <v>483954</v>
       </c>
       <c r="R69" t="n">
-        <v>7019708</v>
+        <v>7019556</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120420834</v>
+        <v>120420833</v>
       </c>
       <c r="B70" t="n">
         <v>78542</v>
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483657</v>
+        <v>483556</v>
       </c>
       <c r="R70" t="n">
-        <v>7019712</v>
+        <v>7019737</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305416</v>
+        <v>120305425</v>
       </c>
       <c r="B11" t="n">
-        <v>74638</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,25 +1649,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483989</v>
+        <v>483637</v>
       </c>
       <c r="R11" t="n">
-        <v>7019538</v>
+        <v>7019655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305425</v>
+        <v>120305416</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>74638</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483637</v>
+        <v>483989</v>
       </c>
       <c r="R12" t="n">
-        <v>7019655</v>
+        <v>7019538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305462</v>
+        <v>120305415</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>74638</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3362,25 +3362,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483700</v>
+        <v>483864</v>
       </c>
       <c r="R27" t="n">
-        <v>7019608</v>
+        <v>7019545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305415</v>
+        <v>120305462</v>
       </c>
       <c r="B28" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483864</v>
+        <v>483700</v>
       </c>
       <c r="R28" t="n">
-        <v>7019545</v>
+        <v>7019608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6708,10 +6708,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120420877</v>
+        <v>120420832</v>
       </c>
       <c r="B59" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483497</v>
+        <v>483500</v>
       </c>
       <c r="R59" t="n">
-        <v>7019675</v>
+        <v>7019677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6814,10 +6814,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120420832</v>
+        <v>120420836</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6830,21 +6830,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483500</v>
+        <v>483663</v>
       </c>
       <c r="R60" t="n">
-        <v>7019677</v>
+        <v>7019709</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120420836</v>
+        <v>120420877</v>
       </c>
       <c r="B61" t="n">
-        <v>90598</v>
+        <v>95478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483663</v>
+        <v>483497</v>
       </c>
       <c r="R61" t="n">
-        <v>7019709</v>
+        <v>7019675</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120305214</v>
+        <v>120305234</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483756</v>
+        <v>483609</v>
       </c>
       <c r="R2" t="n">
-        <v>7019560</v>
+        <v>7019727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,12 +760,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lurigt växtsätt inuti hålighet på gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305171</v>
+        <v>120305355</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483590</v>
+        <v>483741</v>
       </c>
       <c r="R3" t="n">
-        <v>7019723</v>
+        <v>7019614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305355</v>
+        <v>120305353</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -939,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483741</v>
+        <v>483754</v>
       </c>
       <c r="R4" t="n">
-        <v>7019614</v>
+        <v>7019590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305296</v>
+        <v>120305416</v>
       </c>
       <c r="B5" t="n">
-        <v>96885</v>
+        <v>74638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483979</v>
+        <v>483989</v>
       </c>
       <c r="R5" t="n">
-        <v>7019514</v>
+        <v>7019538</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305172</v>
+        <v>120305244</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>79527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1120,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483662</v>
+        <v>483828</v>
       </c>
       <c r="R6" t="n">
-        <v>7019676</v>
+        <v>7019588</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120305463</v>
+        <v>120305439</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1257,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483849</v>
+        <v>483782</v>
       </c>
       <c r="R7" t="n">
-        <v>7019545</v>
+        <v>7019560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305297</v>
+        <v>120305195</v>
       </c>
       <c r="B8" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,25 +1332,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1363,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484003</v>
+        <v>483673</v>
       </c>
       <c r="R8" t="n">
-        <v>7019580</v>
+        <v>7019675</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1531,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305432</v>
+        <v>120305463</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1575,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483629</v>
+        <v>483849</v>
       </c>
       <c r="R10" t="n">
-        <v>7019655</v>
+        <v>7019545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305425</v>
+        <v>120305354</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,25 +1650,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483637</v>
+        <v>483639</v>
       </c>
       <c r="R11" t="n">
-        <v>7019655</v>
+        <v>7019659</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305416</v>
+        <v>120305196</v>
       </c>
       <c r="B12" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1756,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483989</v>
+        <v>483658</v>
       </c>
       <c r="R12" t="n">
-        <v>7019538</v>
+        <v>7019677</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305320</v>
+        <v>120305432</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1893,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483836</v>
+        <v>483629</v>
       </c>
       <c r="R13" t="n">
-        <v>7019556</v>
+        <v>7019655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305244</v>
+        <v>120305462</v>
       </c>
       <c r="B14" t="n">
-        <v>79527</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,25 +1968,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1999,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483828</v>
+        <v>483700</v>
       </c>
       <c r="R14" t="n">
-        <v>7019588</v>
+        <v>7019608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2062,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305354</v>
+        <v>120305404</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2105,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483639</v>
+        <v>483788</v>
       </c>
       <c r="R15" t="n">
-        <v>7019659</v>
+        <v>7019601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305278</v>
+        <v>120305296</v>
       </c>
       <c r="B16" t="n">
         <v>96885</v>
@@ -2211,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483813</v>
+        <v>483979</v>
       </c>
       <c r="R16" t="n">
-        <v>7019540</v>
+        <v>7019514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305439</v>
+        <v>120305213</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,21 +2290,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2317,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483782</v>
+        <v>483661</v>
       </c>
       <c r="R17" t="n">
-        <v>7019560</v>
+        <v>7019669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120305464</v>
+        <v>120305278</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,25 +2392,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2423,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483889</v>
+        <v>483813</v>
       </c>
       <c r="R18" t="n">
-        <v>7019544</v>
+        <v>7019540</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305404</v>
+        <v>120305464</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,25 +2498,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2529,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483788</v>
+        <v>483889</v>
       </c>
       <c r="R19" t="n">
-        <v>7019601</v>
+        <v>7019544</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305353</v>
+        <v>120305320</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,25 +2604,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2635,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483754</v>
+        <v>483836</v>
       </c>
       <c r="R20" t="n">
-        <v>7019590</v>
+        <v>7019556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305295</v>
+        <v>120305214</v>
       </c>
       <c r="B21" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,25 +2710,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2735,16 +2736,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483819</v>
+        <v>483756</v>
       </c>
       <c r="R21" t="n">
-        <v>7019570</v>
+        <v>7019560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,10 +2812,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305215</v>
+        <v>120305172</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,21 +2828,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2841,24 +2850,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483868</v>
+        <v>483662</v>
       </c>
       <c r="R22" t="n">
-        <v>7019544</v>
+        <v>7019676</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305234</v>
+        <v>120305425</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2934,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2955,19 +2956,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483609</v>
+        <v>483637</v>
       </c>
       <c r="R23" t="n">
-        <v>7019727</v>
+        <v>7019655</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,18 +3000,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lurigt växtsätt inuti hålighet på gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3032,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120305196</v>
+        <v>120305297</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,25 +3036,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3076,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483658</v>
+        <v>484003</v>
       </c>
       <c r="R24" t="n">
-        <v>7019677</v>
+        <v>7019580</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305195</v>
+        <v>120305415</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>74638</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,25 +3142,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3182,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483673</v>
+        <v>483864</v>
       </c>
       <c r="R25" t="n">
-        <v>7019675</v>
+        <v>7019545</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3236,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305213</v>
+        <v>120305215</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3282,16 +3274,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483661</v>
+        <v>483868</v>
       </c>
       <c r="R26" t="n">
-        <v>7019669</v>
+        <v>7019544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305415</v>
+        <v>120305295</v>
       </c>
       <c r="B27" t="n">
-        <v>74638</v>
+        <v>96885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483864</v>
+        <v>483819</v>
       </c>
       <c r="R27" t="n">
-        <v>7019545</v>
+        <v>7019570</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305462</v>
+        <v>120305171</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483700</v>
+        <v>483590</v>
       </c>
       <c r="R28" t="n">
-        <v>7019608</v>
+        <v>7019723</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120383857</v>
+        <v>120382600</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,34 +3578,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vågen, Vågen, Jmt</t>
+          <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483696</v>
+        <v>483535</v>
       </c>
       <c r="R29" t="n">
-        <v>7019783</v>
+        <v>7019649</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120382563</v>
+        <v>120383857</v>
       </c>
       <c r="B30" t="n">
-        <v>90576</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3680,34 +3680,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Indalsälven, Indalsälven, Jmt</t>
+          <t>Vågen, Vågen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483510</v>
+        <v>483696</v>
       </c>
       <c r="R30" t="n">
-        <v>7019662</v>
+        <v>7019783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120382600</v>
+        <v>120382563</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3898,21 +3898,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483535</v>
+        <v>483510</v>
       </c>
       <c r="R32" t="n">
-        <v>7019649</v>
+        <v>7019662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120408134</v>
+        <v>120408123</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>484009</v>
+        <v>483474</v>
       </c>
       <c r="R34" t="n">
-        <v>7019590</v>
+        <v>7019669</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4162,6 +4162,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4188,10 +4193,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120408141</v>
+        <v>120408127</v>
       </c>
       <c r="B35" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4204,21 +4209,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4233,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483464</v>
+        <v>483461</v>
       </c>
       <c r="R35" t="n">
-        <v>7019618</v>
+        <v>7019658</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4264,6 +4269,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4290,10 +4300,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120408135</v>
+        <v>120408125</v>
       </c>
       <c r="B36" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4306,21 +4316,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4340,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483713</v>
+        <v>483456</v>
       </c>
       <c r="R36" t="n">
-        <v>7019760</v>
+        <v>7019660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4366,6 +4376,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4392,10 +4407,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120408128</v>
+        <v>120408135</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4408,21 +4423,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4432,10 +4447,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483452</v>
+        <v>483713</v>
       </c>
       <c r="R37" t="n">
-        <v>7019647</v>
+        <v>7019760</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4468,11 +4483,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4499,10 +4509,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120408138</v>
+        <v>120408128</v>
       </c>
       <c r="B38" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4515,21 +4525,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4539,10 +4549,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483468</v>
+        <v>483452</v>
       </c>
       <c r="R38" t="n">
-        <v>7019617</v>
+        <v>7019647</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4575,6 +4585,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4601,10 +4616,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120408123</v>
+        <v>120408116</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4617,21 +4632,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4641,10 +4656,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483474</v>
+        <v>483550</v>
       </c>
       <c r="R39" t="n">
-        <v>7019669</v>
+        <v>7019749</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,11 +4692,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4708,10 +4718,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120408125</v>
+        <v>120408133</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4724,21 +4734,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4748,10 +4758,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483456</v>
+        <v>484009</v>
       </c>
       <c r="R40" t="n">
-        <v>7019660</v>
+        <v>7019588</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,11 +4794,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4815,10 +4820,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120408144</v>
+        <v>120408117</v>
       </c>
       <c r="B41" t="n">
-        <v>82321</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4831,21 +4836,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4855,10 +4860,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483550</v>
+        <v>483561</v>
       </c>
       <c r="R41" t="n">
-        <v>7019749</v>
+        <v>7019762</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4899,7 +4904,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4918,7 +4922,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120408127</v>
+        <v>120408121</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4958,10 +4962,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483461</v>
+        <v>483627</v>
       </c>
       <c r="R42" t="n">
-        <v>7019658</v>
+        <v>7019822</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,10 +5029,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120408133</v>
+        <v>120408137</v>
       </c>
       <c r="B43" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5041,21 +5045,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5065,10 +5069,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484009</v>
+        <v>483624</v>
       </c>
       <c r="R43" t="n">
-        <v>7019588</v>
+        <v>7019813</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,10 +5131,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120408121</v>
+        <v>120408134</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5143,21 +5147,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5167,10 +5171,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483627</v>
+        <v>484009</v>
       </c>
       <c r="R44" t="n">
-        <v>7019822</v>
+        <v>7019590</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,11 +5207,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5341,10 +5340,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120408124</v>
+        <v>120408144</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,21 +5356,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5381,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483470</v>
+        <v>483550</v>
       </c>
       <c r="R46" t="n">
-        <v>7019656</v>
+        <v>7019749</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5419,17 +5418,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5448,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120408122</v>
+        <v>120408143</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5464,21 +5459,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5488,10 +5483,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483606</v>
+        <v>483743</v>
       </c>
       <c r="R47" t="n">
-        <v>7019790</v>
+        <v>7019735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,17 +5521,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5555,10 +5546,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120408116</v>
+        <v>120408122</v>
       </c>
       <c r="B48" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5571,21 +5562,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5595,10 +5586,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483550</v>
+        <v>483606</v>
       </c>
       <c r="R48" t="n">
-        <v>7019749</v>
+        <v>7019790</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5631,6 +5622,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5657,10 +5653,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120408117</v>
+        <v>120408124</v>
       </c>
       <c r="B49" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5673,21 +5669,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5697,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483561</v>
+        <v>483470</v>
       </c>
       <c r="R49" t="n">
-        <v>7019762</v>
+        <v>7019656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5733,6 +5729,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5759,7 +5760,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120408137</v>
+        <v>120408138</v>
       </c>
       <c r="B50" t="n">
         <v>79623</v>
@@ -5799,10 +5800,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483624</v>
+        <v>483468</v>
       </c>
       <c r="R50" t="n">
-        <v>7019813</v>
+        <v>7019617</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5861,10 +5862,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120408143</v>
+        <v>120408132</v>
       </c>
       <c r="B51" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5877,21 +5878,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5901,10 +5902,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483743</v>
+        <v>483589</v>
       </c>
       <c r="R51" t="n">
-        <v>7019735</v>
+        <v>7019600</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5939,13 +5940,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5964,10 +5969,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120408118</v>
+        <v>120408141</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5980,21 +5985,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6004,10 +6009,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483476</v>
+        <v>483464</v>
       </c>
       <c r="R52" t="n">
-        <v>7019660</v>
+        <v>7019618</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6040,11 +6045,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6071,7 +6071,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120408132</v>
+        <v>120408118</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483589</v>
+        <v>483476</v>
       </c>
       <c r="R53" t="n">
-        <v>7019600</v>
+        <v>7019660</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,10 +6178,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120420872</v>
+        <v>120420878</v>
       </c>
       <c r="B54" t="n">
-        <v>87409</v>
+        <v>95478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4405</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483619</v>
+        <v>483767</v>
       </c>
       <c r="R54" t="n">
-        <v>7019709</v>
+        <v>7019702</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120420835</v>
+        <v>120420883</v>
       </c>
       <c r="B56" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483638</v>
+        <v>483664</v>
       </c>
       <c r="R56" t="n">
-        <v>7019659</v>
+        <v>7019708</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6489,17 +6489,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120420883</v>
+        <v>120420849</v>
       </c>
       <c r="B57" t="n">
-        <v>90576</v>
+        <v>79652</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6508,25 +6508,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483664</v>
+        <v>483572</v>
       </c>
       <c r="R57" t="n">
-        <v>7019708</v>
+        <v>7019741</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6602,10 +6602,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120420834</v>
+        <v>120420836</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6618,21 +6618,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483657</v>
+        <v>483663</v>
       </c>
       <c r="R58" t="n">
-        <v>7019712</v>
+        <v>7019709</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6708,10 +6708,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120420832</v>
+        <v>120420837</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483500</v>
+        <v>483750</v>
       </c>
       <c r="R59" t="n">
-        <v>7019677</v>
+        <v>7019734</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6814,10 +6814,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120420836</v>
+        <v>120420840</v>
       </c>
       <c r="B60" t="n">
-        <v>90598</v>
+        <v>74638</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6826,25 +6826,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483663</v>
+        <v>483762</v>
       </c>
       <c r="R60" t="n">
-        <v>7019709</v>
+        <v>7019692</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120420877</v>
+        <v>120420844</v>
       </c>
       <c r="B61" t="n">
-        <v>95478</v>
+        <v>96885</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6932,25 +6932,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483497</v>
+        <v>483852</v>
       </c>
       <c r="R61" t="n">
-        <v>7019675</v>
+        <v>7019773</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120420849</v>
+        <v>120420877</v>
       </c>
       <c r="B62" t="n">
-        <v>79652</v>
+        <v>95478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7038,25 +7038,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483572</v>
+        <v>483497</v>
       </c>
       <c r="R62" t="n">
-        <v>7019741</v>
+        <v>7019675</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7125,17 +7125,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120420878</v>
+        <v>120420835</v>
       </c>
       <c r="B63" t="n">
-        <v>95478</v>
+        <v>90598</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7148,21 +7148,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483767</v>
+        <v>483638</v>
       </c>
       <c r="R63" t="n">
-        <v>7019702</v>
+        <v>7019659</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120420887</v>
+        <v>120420830</v>
       </c>
       <c r="B64" t="n">
-        <v>87423</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483979</v>
+        <v>483954</v>
       </c>
       <c r="R64" t="n">
-        <v>7019620</v>
+        <v>7019556</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120420837</v>
+        <v>120420887</v>
       </c>
       <c r="B65" t="n">
-        <v>74646</v>
+        <v>87423</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>308</v>
+        <v>4412</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483750</v>
+        <v>483979</v>
       </c>
       <c r="R65" t="n">
-        <v>7019734</v>
+        <v>7019620</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7443,17 +7443,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120420840</v>
+        <v>120420872</v>
       </c>
       <c r="B66" t="n">
-        <v>74638</v>
+        <v>87409</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7466,21 +7466,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6439</v>
+        <v>4405</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483762</v>
+        <v>483619</v>
       </c>
       <c r="R66" t="n">
-        <v>7019692</v>
+        <v>7019709</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7549,17 +7549,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120420844</v>
+        <v>120420833</v>
       </c>
       <c r="B67" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7568,25 +7568,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483852</v>
+        <v>483556</v>
       </c>
       <c r="R67" t="n">
-        <v>7019773</v>
+        <v>7019737</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120420830</v>
+        <v>120420834</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483954</v>
+        <v>483657</v>
       </c>
       <c r="R69" t="n">
-        <v>7019556</v>
+        <v>7019712</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120420833</v>
+        <v>120420832</v>
       </c>
       <c r="B70" t="n">
         <v>78542</v>
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483556</v>
+        <v>483500</v>
       </c>
       <c r="R70" t="n">
-        <v>7019737</v>
+        <v>7019677</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120305234</v>
+        <v>120305416</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>74638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483609</v>
+        <v>483989</v>
       </c>
       <c r="R2" t="n">
-        <v>7019727</v>
+        <v>7019538</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,18 +757,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lurigt växtsätt inuti hålighet på gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305355</v>
+        <v>120305433</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483741</v>
+        <v>483702</v>
       </c>
       <c r="R3" t="n">
-        <v>7019614</v>
+        <v>7019609</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305353</v>
+        <v>120305404</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -940,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483754</v>
+        <v>483788</v>
       </c>
       <c r="R4" t="n">
-        <v>7019590</v>
+        <v>7019601</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305416</v>
+        <v>120305278</v>
       </c>
       <c r="B5" t="n">
-        <v>74638</v>
+        <v>96885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1046,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483989</v>
+        <v>483813</v>
       </c>
       <c r="R5" t="n">
-        <v>7019538</v>
+        <v>7019540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305244</v>
+        <v>120305439</v>
       </c>
       <c r="B6" t="n">
-        <v>79527</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483828</v>
+        <v>483782</v>
       </c>
       <c r="R6" t="n">
-        <v>7019588</v>
+        <v>7019560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120305439</v>
+        <v>120305214</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1252,13 +1243,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483782</v>
+        <v>483756</v>
       </c>
       <c r="R7" t="n">
         <v>7019560</v>
@@ -1320,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305195</v>
+        <v>120305320</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1364,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483673</v>
+        <v>483836</v>
       </c>
       <c r="R8" t="n">
-        <v>7019675</v>
+        <v>7019556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305433</v>
+        <v>120305425</v>
       </c>
       <c r="B9" t="n">
         <v>90598</v>
@@ -1470,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483702</v>
+        <v>483637</v>
       </c>
       <c r="R9" t="n">
-        <v>7019609</v>
+        <v>7019655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305463</v>
+        <v>120305234</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1570,16 +1569,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483849</v>
+        <v>483609</v>
       </c>
       <c r="R10" t="n">
-        <v>7019545</v>
+        <v>7019727</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,12 +1616,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lurigt växtsätt inuti hålighet på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1638,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305354</v>
+        <v>120305244</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>79527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,25 +1658,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483639</v>
+        <v>483828</v>
       </c>
       <c r="R11" t="n">
-        <v>7019659</v>
+        <v>7019588</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1752,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305196</v>
+        <v>120305171</v>
       </c>
       <c r="B12" t="n">
         <v>90580</v>
@@ -1788,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483658</v>
+        <v>483590</v>
       </c>
       <c r="R12" t="n">
-        <v>7019677</v>
+        <v>7019723</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305432</v>
+        <v>120305297</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>96885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1870,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1894,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483629</v>
+        <v>484003</v>
       </c>
       <c r="R13" t="n">
-        <v>7019655</v>
+        <v>7019580</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305462</v>
+        <v>120305355</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,25 +1976,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2000,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483700</v>
+        <v>483741</v>
       </c>
       <c r="R14" t="n">
-        <v>7019608</v>
+        <v>7019614</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305404</v>
+        <v>120305215</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,25 +2082,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2100,16 +2108,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483788</v>
+        <v>483868</v>
       </c>
       <c r="R15" t="n">
-        <v>7019601</v>
+        <v>7019544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305296</v>
+        <v>120305432</v>
       </c>
       <c r="B16" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,25 +2196,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2212,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483979</v>
+        <v>483629</v>
       </c>
       <c r="R16" t="n">
-        <v>7019514</v>
+        <v>7019655</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305213</v>
+        <v>120305353</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,25 +2302,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2318,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483661</v>
+        <v>483754</v>
       </c>
       <c r="R17" t="n">
-        <v>7019669</v>
+        <v>7019590</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120305278</v>
+        <v>120305213</v>
       </c>
       <c r="B18" t="n">
-        <v>96885</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,25 +2408,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2424,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483813</v>
+        <v>483661</v>
       </c>
       <c r="R18" t="n">
-        <v>7019540</v>
+        <v>7019669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305464</v>
+        <v>120305196</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483889</v>
+        <v>483658</v>
       </c>
       <c r="R19" t="n">
-        <v>7019544</v>
+        <v>7019677</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305320</v>
+        <v>120305295</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,25 +2620,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483836</v>
+        <v>483819</v>
       </c>
       <c r="R20" t="n">
-        <v>7019556</v>
+        <v>7019570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305214</v>
+        <v>120305463</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2730,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2736,24 +2752,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483756</v>
+        <v>483849</v>
       </c>
       <c r="R21" t="n">
-        <v>7019560</v>
+        <v>7019545</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305172</v>
+        <v>120305296</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2824,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2856,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483662</v>
+        <v>483979</v>
       </c>
       <c r="R22" t="n">
-        <v>7019676</v>
+        <v>7019514</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305425</v>
+        <v>120305464</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2934,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2962,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483637</v>
+        <v>483889</v>
       </c>
       <c r="R23" t="n">
-        <v>7019655</v>
+        <v>7019544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120305297</v>
+        <v>120305354</v>
       </c>
       <c r="B24" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3036,25 +3044,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3068,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>484003</v>
+        <v>483639</v>
       </c>
       <c r="R24" t="n">
-        <v>7019580</v>
+        <v>7019659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305415</v>
+        <v>120305172</v>
       </c>
       <c r="B25" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,25 +3150,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3174,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483864</v>
+        <v>483662</v>
       </c>
       <c r="R25" t="n">
-        <v>7019545</v>
+        <v>7019676</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3236,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305215</v>
+        <v>120305195</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3252,21 +3260,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3274,24 +3282,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483868</v>
+        <v>483673</v>
       </c>
       <c r="R26" t="n">
-        <v>7019544</v>
+        <v>7019675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305295</v>
+        <v>120305415</v>
       </c>
       <c r="B27" t="n">
-        <v>96885</v>
+        <v>74638</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483819</v>
+        <v>483864</v>
       </c>
       <c r="R27" t="n">
-        <v>7019570</v>
+        <v>7019545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305171</v>
+        <v>120305462</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483590</v>
+        <v>483700</v>
       </c>
       <c r="R28" t="n">
-        <v>7019723</v>
+        <v>7019608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120382600</v>
+        <v>120382563</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483535</v>
+        <v>483510</v>
       </c>
       <c r="R29" t="n">
-        <v>7019649</v>
+        <v>7019662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120383857</v>
+        <v>120382600</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3680,34 +3680,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vågen, Vågen, Jmt</t>
+          <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483696</v>
+        <v>483535</v>
       </c>
       <c r="R30" t="n">
-        <v>7019783</v>
+        <v>7019649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120383186</v>
+        <v>120383857</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3782,48 +3782,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Indalsälven, Indalsälven, Jmt</t>
+          <t>Vågen, Vågen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483495</v>
+        <v>483696</v>
       </c>
       <c r="R31" t="n">
-        <v>7019685</v>
+        <v>7019783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3882,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120382563</v>
+        <v>120383186</v>
       </c>
       <c r="B32" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3898,34 +3884,48 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483510</v>
+        <v>483495</v>
       </c>
       <c r="R32" t="n">
-        <v>7019662</v>
+        <v>7019685</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120408123</v>
+        <v>120408137</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483474</v>
+        <v>483624</v>
       </c>
       <c r="R34" t="n">
-        <v>7019669</v>
+        <v>7019813</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4162,11 +4162,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4193,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120408127</v>
+        <v>120408138</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4209,21 +4204,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4233,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483461</v>
+        <v>483468</v>
       </c>
       <c r="R35" t="n">
-        <v>7019658</v>
+        <v>7019617</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4269,11 +4264,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4300,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120408125</v>
+        <v>120408117</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4316,21 +4306,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4340,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483456</v>
+        <v>483561</v>
       </c>
       <c r="R36" t="n">
-        <v>7019660</v>
+        <v>7019762</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4376,11 +4366,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4407,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120408135</v>
+        <v>120408118</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4423,21 +4408,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4447,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483713</v>
+        <v>483476</v>
       </c>
       <c r="R37" t="n">
-        <v>7019760</v>
+        <v>7019660</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4483,6 +4468,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4509,10 +4499,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120408128</v>
+        <v>120408144</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4525,21 +4515,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4549,10 +4539,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483452</v>
+        <v>483550</v>
       </c>
       <c r="R38" t="n">
-        <v>7019647</v>
+        <v>7019749</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,17 +4577,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4616,10 +4602,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120408116</v>
+        <v>120408122</v>
       </c>
       <c r="B39" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4632,21 +4618,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4656,10 +4642,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483550</v>
+        <v>483606</v>
       </c>
       <c r="R39" t="n">
-        <v>7019749</v>
+        <v>7019790</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4692,6 +4678,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120408133</v>
+        <v>120408132</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4734,21 +4725,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4758,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>484009</v>
+        <v>483589</v>
       </c>
       <c r="R40" t="n">
-        <v>7019588</v>
+        <v>7019600</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,6 +4785,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4820,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120408117</v>
+        <v>120408135</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4836,21 +4832,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4860,10 +4856,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483561</v>
+        <v>483713</v>
       </c>
       <c r="R41" t="n">
-        <v>7019762</v>
+        <v>7019760</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4922,10 +4918,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120408121</v>
+        <v>120408143</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4938,21 +4934,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4962,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483627</v>
+        <v>483743</v>
       </c>
       <c r="R42" t="n">
-        <v>7019822</v>
+        <v>7019735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5000,17 +4996,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5029,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120408137</v>
+        <v>120408128</v>
       </c>
       <c r="B43" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5045,21 +5037,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5069,10 +5061,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483624</v>
+        <v>483452</v>
       </c>
       <c r="R43" t="n">
-        <v>7019813</v>
+        <v>7019647</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5105,6 +5097,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5131,10 +5128,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120408134</v>
+        <v>120408116</v>
       </c>
       <c r="B44" t="n">
-        <v>79623</v>
+        <v>74654</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5147,21 +5144,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5171,10 +5168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484009</v>
+        <v>483550</v>
       </c>
       <c r="R44" t="n">
-        <v>7019590</v>
+        <v>7019749</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5233,7 +5230,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120408131</v>
+        <v>120408124</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5273,10 +5270,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483548</v>
+        <v>483470</v>
       </c>
       <c r="R45" t="n">
-        <v>7019602</v>
+        <v>7019656</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5340,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120408144</v>
+        <v>120408123</v>
       </c>
       <c r="B46" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5356,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5377,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483550</v>
+        <v>483474</v>
       </c>
       <c r="R46" t="n">
-        <v>7019749</v>
+        <v>7019669</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,13 +5415,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5443,10 +5444,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120408143</v>
+        <v>120408133</v>
       </c>
       <c r="B47" t="n">
-        <v>82321</v>
+        <v>79624</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,21 +5460,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5483,10 +5484,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483743</v>
+        <v>484009</v>
       </c>
       <c r="R47" t="n">
-        <v>7019735</v>
+        <v>7019588</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5527,7 +5528,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120408122</v>
+        <v>120408127</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483606</v>
+        <v>483461</v>
       </c>
       <c r="R48" t="n">
-        <v>7019790</v>
+        <v>7019658</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120408124</v>
+        <v>120408141</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5669,21 +5669,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483470</v>
+        <v>483464</v>
       </c>
       <c r="R49" t="n">
-        <v>7019656</v>
+        <v>7019618</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5729,11 +5729,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5760,7 +5755,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120408138</v>
+        <v>120408134</v>
       </c>
       <c r="B50" t="n">
         <v>79623</v>
@@ -5800,10 +5795,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483468</v>
+        <v>484009</v>
       </c>
       <c r="R50" t="n">
-        <v>7019617</v>
+        <v>7019590</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5862,7 +5857,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120408132</v>
+        <v>120408121</v>
       </c>
       <c r="B51" t="n">
         <v>57320</v>
@@ -5902,10 +5897,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483589</v>
+        <v>483627</v>
       </c>
       <c r="R51" t="n">
-        <v>7019600</v>
+        <v>7019822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5942,7 +5937,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5969,10 +5964,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120408141</v>
+        <v>120408125</v>
       </c>
       <c r="B52" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5985,21 +5980,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6009,10 +6004,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483464</v>
+        <v>483456</v>
       </c>
       <c r="R52" t="n">
-        <v>7019618</v>
+        <v>7019660</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6045,6 +6040,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6071,7 +6071,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120408118</v>
+        <v>120408131</v>
       </c>
       <c r="B53" t="n">
         <v>57320</v>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483476</v>
+        <v>483548</v>
       </c>
       <c r="R53" t="n">
-        <v>7019660</v>
+        <v>7019602</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,10 +6178,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120420878</v>
+        <v>120420830</v>
       </c>
       <c r="B54" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,21 +6194,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483767</v>
+        <v>483954</v>
       </c>
       <c r="R54" t="n">
-        <v>7019702</v>
+        <v>7019556</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6277,17 +6277,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120420838</v>
+        <v>120420872</v>
       </c>
       <c r="B55" t="n">
-        <v>74646</v>
+        <v>87409</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6296,25 +6296,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>308</v>
+        <v>4405</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483758</v>
+        <v>483619</v>
       </c>
       <c r="R55" t="n">
-        <v>7019694</v>
+        <v>7019709</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120420883</v>
+        <v>120420837</v>
       </c>
       <c r="B56" t="n">
-        <v>90576</v>
+        <v>74646</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483664</v>
+        <v>483750</v>
       </c>
       <c r="R56" t="n">
-        <v>7019708</v>
+        <v>7019734</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6489,17 +6489,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120420849</v>
+        <v>120420840</v>
       </c>
       <c r="B57" t="n">
-        <v>79652</v>
+        <v>74638</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483572</v>
+        <v>483762</v>
       </c>
       <c r="R57" t="n">
-        <v>7019741</v>
+        <v>7019692</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6602,10 +6602,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120420836</v>
+        <v>120420834</v>
       </c>
       <c r="B58" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6618,21 +6618,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483663</v>
+        <v>483657</v>
       </c>
       <c r="R58" t="n">
-        <v>7019709</v>
+        <v>7019712</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120420837</v>
+        <v>120420838</v>
       </c>
       <c r="B59" t="n">
         <v>74646</v>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483750</v>
+        <v>483758</v>
       </c>
       <c r="R59" t="n">
-        <v>7019734</v>
+        <v>7019694</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6814,10 +6814,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120420840</v>
+        <v>120420849</v>
       </c>
       <c r="B60" t="n">
-        <v>74638</v>
+        <v>79652</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6830,21 +6830,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483762</v>
+        <v>483572</v>
       </c>
       <c r="R60" t="n">
-        <v>7019692</v>
+        <v>7019741</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120420844</v>
+        <v>120420887</v>
       </c>
       <c r="B61" t="n">
-        <v>96885</v>
+        <v>87423</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6932,25 +6932,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>4412</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483852</v>
+        <v>483979</v>
       </c>
       <c r="R61" t="n">
-        <v>7019773</v>
+        <v>7019620</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120420877</v>
+        <v>120420832</v>
       </c>
       <c r="B62" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483497</v>
+        <v>483500</v>
       </c>
       <c r="R62" t="n">
-        <v>7019675</v>
+        <v>7019677</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7125,17 +7125,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120420835</v>
+        <v>120420877</v>
       </c>
       <c r="B63" t="n">
-        <v>90598</v>
+        <v>95478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7148,21 +7148,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483638</v>
+        <v>483497</v>
       </c>
       <c r="R63" t="n">
-        <v>7019659</v>
+        <v>7019675</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120420830</v>
+        <v>120420833</v>
       </c>
       <c r="B64" t="n">
         <v>78542</v>
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483954</v>
+        <v>483556</v>
       </c>
       <c r="R64" t="n">
-        <v>7019556</v>
+        <v>7019737</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120420887</v>
+        <v>120420831</v>
       </c>
       <c r="B65" t="n">
-        <v>87423</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483979</v>
+        <v>483607</v>
       </c>
       <c r="R65" t="n">
-        <v>7019620</v>
+        <v>7019631</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7443,17 +7443,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120420872</v>
+        <v>120420878</v>
       </c>
       <c r="B66" t="n">
-        <v>87409</v>
+        <v>95478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7462,25 +7462,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4405</v>
+        <v>53</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483619</v>
+        <v>483767</v>
       </c>
       <c r="R66" t="n">
-        <v>7019709</v>
+        <v>7019702</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7549,17 +7549,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120420833</v>
+        <v>120420883</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7572,21 +7572,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483556</v>
+        <v>483664</v>
       </c>
       <c r="R67" t="n">
-        <v>7019737</v>
+        <v>7019708</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120420831</v>
+        <v>120420835</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7678,21 +7678,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483607</v>
+        <v>483638</v>
       </c>
       <c r="R68" t="n">
-        <v>7019631</v>
+        <v>7019659</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7768,10 +7768,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120420834</v>
+        <v>120420844</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7780,25 +7780,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483657</v>
+        <v>483852</v>
       </c>
       <c r="R69" t="n">
-        <v>7019712</v>
+        <v>7019773</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120420832</v>
+        <v>120420836</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7890,21 +7890,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483500</v>
+        <v>483663</v>
       </c>
       <c r="R70" t="n">
-        <v>7019677</v>
+        <v>7019709</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305433</v>
+        <v>120305214</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,16 +819,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483702</v>
+        <v>483756</v>
       </c>
       <c r="R3" t="n">
-        <v>7019609</v>
+        <v>7019560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305404</v>
+        <v>120305433</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483788</v>
+        <v>483702</v>
       </c>
       <c r="R4" t="n">
-        <v>7019601</v>
+        <v>7019609</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305278</v>
+        <v>120305439</v>
       </c>
       <c r="B5" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483813</v>
+        <v>483782</v>
       </c>
       <c r="R5" t="n">
-        <v>7019540</v>
+        <v>7019560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305439</v>
+        <v>120305404</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1119,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483782</v>
+        <v>483788</v>
       </c>
       <c r="R6" t="n">
-        <v>7019560</v>
+        <v>7019601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120305214</v>
+        <v>120305278</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1225,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,24 +1251,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483756</v>
+        <v>483813</v>
       </c>
       <c r="R7" t="n">
-        <v>7019560</v>
+        <v>7019540</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305195</v>
+        <v>120305415</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>74638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483673</v>
+        <v>483864</v>
       </c>
       <c r="R26" t="n">
-        <v>7019675</v>
+        <v>7019545</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305415</v>
+        <v>120305462</v>
       </c>
       <c r="B27" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3362,25 +3362,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483864</v>
+        <v>483700</v>
       </c>
       <c r="R27" t="n">
-        <v>7019545</v>
+        <v>7019608</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305462</v>
+        <v>120305195</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483700</v>
+        <v>483673</v>
       </c>
       <c r="R28" t="n">
-        <v>7019608</v>
+        <v>7019675</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120408138</v>
+        <v>120408117</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483468</v>
+        <v>483561</v>
       </c>
       <c r="R35" t="n">
-        <v>7019617</v>
+        <v>7019762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120408117</v>
+        <v>120408118</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483561</v>
+        <v>483476</v>
       </c>
       <c r="R36" t="n">
-        <v>7019762</v>
+        <v>7019660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4366,6 +4366,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4392,10 +4397,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120408118</v>
+        <v>120408138</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4408,21 +4413,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4432,10 +4437,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483476</v>
+        <v>483468</v>
       </c>
       <c r="R37" t="n">
-        <v>7019660</v>
+        <v>7019617</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4468,11 +4473,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4918,10 +4918,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120408143</v>
+        <v>120408128</v>
       </c>
       <c r="B42" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4934,21 +4934,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483743</v>
+        <v>483452</v>
       </c>
       <c r="R42" t="n">
-        <v>7019735</v>
+        <v>7019647</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,13 +4996,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5021,10 +5025,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120408128</v>
+        <v>120408143</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5037,21 +5041,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5061,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483452</v>
+        <v>483743</v>
       </c>
       <c r="R43" t="n">
-        <v>7019647</v>
+        <v>7019735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5099,17 +5103,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120420872</v>
+        <v>120420837</v>
       </c>
       <c r="B55" t="n">
-        <v>87409</v>
+        <v>74646</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6296,25 +6296,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4405</v>
+        <v>308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483619</v>
+        <v>483750</v>
       </c>
       <c r="R55" t="n">
-        <v>7019709</v>
+        <v>7019734</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120420837</v>
+        <v>120420872</v>
       </c>
       <c r="B56" t="n">
-        <v>74646</v>
+        <v>87409</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,25 +6402,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>308</v>
+        <v>4405</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483750</v>
+        <v>483619</v>
       </c>
       <c r="R56" t="n">
-        <v>7019734</v>
+        <v>7019709</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7768,10 +7768,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120420844</v>
+        <v>120420836</v>
       </c>
       <c r="B69" t="n">
-        <v>96885</v>
+        <v>90598</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7780,25 +7780,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483852</v>
+        <v>483663</v>
       </c>
       <c r="R69" t="n">
-        <v>7019773</v>
+        <v>7019709</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120420836</v>
+        <v>120420844</v>
       </c>
       <c r="B70" t="n">
-        <v>90598</v>
+        <v>96885</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7886,25 +7886,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483663</v>
+        <v>483852</v>
       </c>
       <c r="R70" t="n">
-        <v>7019709</v>
+        <v>7019773</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120305416</v>
+        <v>120305296</v>
       </c>
       <c r="B2" t="n">
-        <v>74638</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483989</v>
+        <v>483979</v>
       </c>
       <c r="R2" t="n">
-        <v>7019538</v>
+        <v>7019514</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305214</v>
+        <v>120305425</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,24 +819,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483756</v>
+        <v>483637</v>
       </c>
       <c r="R3" t="n">
-        <v>7019560</v>
+        <v>7019655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305433</v>
+        <v>120305320</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483702</v>
+        <v>483836</v>
       </c>
       <c r="R4" t="n">
-        <v>7019609</v>
+        <v>7019556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305439</v>
+        <v>120305353</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483782</v>
+        <v>483754</v>
       </c>
       <c r="R5" t="n">
-        <v>7019560</v>
+        <v>7019590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305404</v>
+        <v>120305439</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483788</v>
+        <v>483782</v>
       </c>
       <c r="R6" t="n">
-        <v>7019601</v>
+        <v>7019560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120305278</v>
+        <v>120305404</v>
       </c>
       <c r="B7" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483813</v>
+        <v>483788</v>
       </c>
       <c r="R7" t="n">
-        <v>7019540</v>
+        <v>7019601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305320</v>
+        <v>120305172</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1363,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483836</v>
+        <v>483662</v>
       </c>
       <c r="R8" t="n">
-        <v>7019556</v>
+        <v>7019676</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305425</v>
+        <v>120305432</v>
       </c>
       <c r="B9" t="n">
         <v>90598</v>
@@ -1469,7 +1461,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483637</v>
+        <v>483629</v>
       </c>
       <c r="R9" t="n">
         <v>7019655</v>
@@ -1531,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305234</v>
+        <v>120305463</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,19 +1561,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483609</v>
+        <v>483849</v>
       </c>
       <c r="R10" t="n">
-        <v>7019727</v>
+        <v>7019545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,18 +1605,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lurigt växtsätt inuti hålighet på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1646,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305244</v>
+        <v>120305196</v>
       </c>
       <c r="B11" t="n">
-        <v>79527</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1690,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483828</v>
+        <v>483658</v>
       </c>
       <c r="R11" t="n">
-        <v>7019588</v>
+        <v>7019677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305171</v>
+        <v>120305215</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1790,16 +1773,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483590</v>
+        <v>483868</v>
       </c>
       <c r="R12" t="n">
-        <v>7019723</v>
+        <v>7019544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1849,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305297</v>
+        <v>120305278</v>
       </c>
       <c r="B13" t="n">
         <v>96885</v>
@@ -1902,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484003</v>
+        <v>483813</v>
       </c>
       <c r="R13" t="n">
-        <v>7019580</v>
+        <v>7019540</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305355</v>
+        <v>120305297</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1976,25 +1967,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2008,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483741</v>
+        <v>484003</v>
       </c>
       <c r="R14" t="n">
-        <v>7019614</v>
+        <v>7019580</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305215</v>
+        <v>120305171</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2108,24 +2099,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483868</v>
+        <v>483590</v>
       </c>
       <c r="R15" t="n">
-        <v>7019544</v>
+        <v>7019723</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305432</v>
+        <v>120305234</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>90527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,21 +2183,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2222,16 +2205,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483629</v>
+        <v>483609</v>
       </c>
       <c r="R16" t="n">
-        <v>7019655</v>
+        <v>7019727</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,12 +2252,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lurigt växtsätt inuti hålighet på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2290,10 +2282,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305353</v>
+        <v>120305244</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>79527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,25 +2294,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2334,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483754</v>
+        <v>483828</v>
       </c>
       <c r="R17" t="n">
-        <v>7019590</v>
+        <v>7019588</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120305213</v>
+        <v>120305214</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2404,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2434,16 +2426,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483661</v>
+        <v>483756</v>
       </c>
       <c r="R18" t="n">
-        <v>7019669</v>
+        <v>7019560</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305196</v>
+        <v>120305355</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483658</v>
+        <v>483741</v>
       </c>
       <c r="R19" t="n">
-        <v>7019677</v>
+        <v>7019614</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305295</v>
+        <v>120305354</v>
       </c>
       <c r="B20" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,25 +2620,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483819</v>
+        <v>483639</v>
       </c>
       <c r="R20" t="n">
-        <v>7019570</v>
+        <v>7019659</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305463</v>
+        <v>120305464</v>
       </c>
       <c r="B21" t="n">
         <v>78542</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483849</v>
+        <v>483889</v>
       </c>
       <c r="R21" t="n">
-        <v>7019545</v>
+        <v>7019544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305296</v>
+        <v>120305415</v>
       </c>
       <c r="B22" t="n">
-        <v>96885</v>
+        <v>74638</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483979</v>
+        <v>483864</v>
       </c>
       <c r="R22" t="n">
-        <v>7019514</v>
+        <v>7019545</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305464</v>
+        <v>120305295</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,25 +2938,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483889</v>
+        <v>483819</v>
       </c>
       <c r="R23" t="n">
-        <v>7019544</v>
+        <v>7019570</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120305354</v>
+        <v>120305462</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483639</v>
+        <v>483700</v>
       </c>
       <c r="R24" t="n">
-        <v>7019659</v>
+        <v>7019608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305172</v>
+        <v>120305416</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>74638</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483662</v>
+        <v>483989</v>
       </c>
       <c r="R25" t="n">
-        <v>7019676</v>
+        <v>7019538</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305415</v>
+        <v>120305195</v>
       </c>
       <c r="B26" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483864</v>
+        <v>483673</v>
       </c>
       <c r="R26" t="n">
-        <v>7019545</v>
+        <v>7019675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305462</v>
+        <v>120305213</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483700</v>
+        <v>483661</v>
       </c>
       <c r="R27" t="n">
-        <v>7019608</v>
+        <v>7019669</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305195</v>
+        <v>120305433</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483673</v>
+        <v>483702</v>
       </c>
       <c r="R28" t="n">
-        <v>7019675</v>
+        <v>7019609</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120382563</v>
+        <v>120382600</v>
       </c>
       <c r="B29" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483510</v>
+        <v>483535</v>
       </c>
       <c r="R29" t="n">
-        <v>7019662</v>
+        <v>7019649</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120382600</v>
+        <v>120383857</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3680,34 +3680,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Indalsälven, Indalsälven, Jmt</t>
+          <t>Vågen, Vågen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483535</v>
+        <v>483696</v>
       </c>
       <c r="R30" t="n">
-        <v>7019649</v>
+        <v>7019783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120383857</v>
+        <v>120383186</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3782,34 +3782,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vågen, Vågen, Jmt</t>
+          <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483696</v>
+        <v>483495</v>
       </c>
       <c r="R31" t="n">
-        <v>7019783</v>
+        <v>7019685</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,10 +3882,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120383186</v>
+        <v>120382563</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,48 +3898,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483495</v>
+        <v>483510</v>
       </c>
       <c r="R32" t="n">
-        <v>7019685</v>
+        <v>7019662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120408118</v>
+        <v>120408121</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483476</v>
+        <v>483627</v>
       </c>
       <c r="R36" t="n">
-        <v>7019660</v>
+        <v>7019822</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4397,10 +4397,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120408138</v>
+        <v>120408128</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483468</v>
+        <v>483452</v>
       </c>
       <c r="R37" t="n">
-        <v>7019617</v>
+        <v>7019647</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4473,6 +4473,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4602,10 +4607,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120408122</v>
+        <v>120408134</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4618,21 +4623,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4642,10 +4647,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483606</v>
+        <v>484009</v>
       </c>
       <c r="R39" t="n">
-        <v>7019790</v>
+        <v>7019590</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,11 +4683,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,7 +4709,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120408132</v>
+        <v>120408124</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483589</v>
+        <v>483470</v>
       </c>
       <c r="R40" t="n">
-        <v>7019600</v>
+        <v>7019656</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120408135</v>
+        <v>120408118</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4832,21 +4832,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483713</v>
+        <v>483476</v>
       </c>
       <c r="R41" t="n">
-        <v>7019760</v>
+        <v>7019660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4892,6 +4892,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4918,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120408128</v>
+        <v>120408125</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -4958,10 +4963,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483452</v>
+        <v>483456</v>
       </c>
       <c r="R42" t="n">
-        <v>7019647</v>
+        <v>7019660</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,10 +5030,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120408143</v>
+        <v>120408122</v>
       </c>
       <c r="B43" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5041,21 +5046,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5065,10 +5070,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483743</v>
+        <v>483606</v>
       </c>
       <c r="R43" t="n">
-        <v>7019735</v>
+        <v>7019790</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5103,13 +5108,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5128,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120408116</v>
+        <v>120408123</v>
       </c>
       <c r="B44" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5144,21 +5153,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5168,10 +5177,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483550</v>
+        <v>483474</v>
       </c>
       <c r="R44" t="n">
-        <v>7019749</v>
+        <v>7019669</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5204,6 +5213,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5230,7 +5244,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120408124</v>
+        <v>120408131</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5270,10 +5284,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483470</v>
+        <v>483548</v>
       </c>
       <c r="R45" t="n">
-        <v>7019656</v>
+        <v>7019602</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,7 +5351,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120408123</v>
+        <v>120408127</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5377,10 +5391,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483474</v>
+        <v>483461</v>
       </c>
       <c r="R46" t="n">
-        <v>7019669</v>
+        <v>7019658</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,7 +5431,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5546,10 +5560,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120408127</v>
+        <v>120408116</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5562,21 +5576,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5586,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483461</v>
+        <v>483550</v>
       </c>
       <c r="R48" t="n">
-        <v>7019658</v>
+        <v>7019749</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5622,11 +5636,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5653,10 +5662,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120408141</v>
+        <v>120408132</v>
       </c>
       <c r="B49" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5669,21 +5678,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5693,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483464</v>
+        <v>483589</v>
       </c>
       <c r="R49" t="n">
-        <v>7019618</v>
+        <v>7019600</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5729,6 +5738,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5755,10 +5769,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120408134</v>
+        <v>120408143</v>
       </c>
       <c r="B50" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5771,21 +5785,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5795,10 +5809,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>484009</v>
+        <v>483743</v>
       </c>
       <c r="R50" t="n">
-        <v>7019590</v>
+        <v>7019735</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5839,6 +5853,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5857,10 +5872,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120408121</v>
+        <v>120408141</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5873,21 +5888,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5897,10 +5912,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483627</v>
+        <v>483464</v>
       </c>
       <c r="R51" t="n">
-        <v>7019822</v>
+        <v>7019618</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5933,11 +5948,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5964,10 +5974,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120408125</v>
+        <v>120408135</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5980,21 +5990,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6004,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483456</v>
+        <v>483713</v>
       </c>
       <c r="R52" t="n">
-        <v>7019660</v>
+        <v>7019760</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6040,11 +6050,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6071,10 +6076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120408131</v>
+        <v>120408138</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6087,21 +6092,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483548</v>
+        <v>483468</v>
       </c>
       <c r="R53" t="n">
-        <v>7019602</v>
+        <v>7019617</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6147,11 +6152,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,10 +6178,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120420830</v>
+        <v>120420883</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,21 +6194,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483954</v>
+        <v>483664</v>
       </c>
       <c r="R54" t="n">
-        <v>7019556</v>
+        <v>7019708</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120420837</v>
+        <v>120420887</v>
       </c>
       <c r="B55" t="n">
-        <v>74646</v>
+        <v>87423</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>308</v>
+        <v>4412</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483750</v>
+        <v>483979</v>
       </c>
       <c r="R55" t="n">
-        <v>7019734</v>
+        <v>7019620</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120420872</v>
+        <v>120420832</v>
       </c>
       <c r="B56" t="n">
-        <v>87409</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,25 +6402,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483619</v>
+        <v>483500</v>
       </c>
       <c r="R56" t="n">
-        <v>7019709</v>
+        <v>7019677</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6496,10 +6496,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120420840</v>
+        <v>120420835</v>
       </c>
       <c r="B57" t="n">
-        <v>74638</v>
+        <v>90598</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6508,25 +6508,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483762</v>
+        <v>483638</v>
       </c>
       <c r="R57" t="n">
-        <v>7019692</v>
+        <v>7019659</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120420834</v>
+        <v>120420830</v>
       </c>
       <c r="B58" t="n">
         <v>78542</v>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483657</v>
+        <v>483954</v>
       </c>
       <c r="R58" t="n">
-        <v>7019712</v>
+        <v>7019556</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6708,10 +6708,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120420838</v>
+        <v>120420872</v>
       </c>
       <c r="B59" t="n">
-        <v>74646</v>
+        <v>87409</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6720,25 +6720,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>4405</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483758</v>
+        <v>483619</v>
       </c>
       <c r="R59" t="n">
-        <v>7019694</v>
+        <v>7019709</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6814,10 +6814,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120420849</v>
+        <v>120420844</v>
       </c>
       <c r="B60" t="n">
-        <v>79652</v>
+        <v>96885</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6830,21 +6830,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483572</v>
+        <v>483852</v>
       </c>
       <c r="R60" t="n">
-        <v>7019741</v>
+        <v>7019773</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120420887</v>
+        <v>120420833</v>
       </c>
       <c r="B61" t="n">
-        <v>87423</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483979</v>
+        <v>483556</v>
       </c>
       <c r="R61" t="n">
-        <v>7019620</v>
+        <v>7019737</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120420832</v>
+        <v>120420837</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483500</v>
+        <v>483750</v>
       </c>
       <c r="R62" t="n">
-        <v>7019677</v>
+        <v>7019734</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120420877</v>
+        <v>120420878</v>
       </c>
       <c r="B63" t="n">
         <v>95478</v>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483497</v>
+        <v>483767</v>
       </c>
       <c r="R63" t="n">
-        <v>7019675</v>
+        <v>7019702</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120420833</v>
+        <v>120420831</v>
       </c>
       <c r="B64" t="n">
         <v>78542</v>
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483556</v>
+        <v>483607</v>
       </c>
       <c r="R64" t="n">
-        <v>7019737</v>
+        <v>7019631</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120420831</v>
+        <v>120420836</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483607</v>
+        <v>483663</v>
       </c>
       <c r="R65" t="n">
-        <v>7019631</v>
+        <v>7019709</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7450,10 +7450,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120420878</v>
+        <v>120420849</v>
       </c>
       <c r="B66" t="n">
-        <v>95478</v>
+        <v>79652</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7462,25 +7462,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483767</v>
+        <v>483572</v>
       </c>
       <c r="R66" t="n">
-        <v>7019702</v>
+        <v>7019741</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7556,10 +7556,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120420883</v>
+        <v>120420840</v>
       </c>
       <c r="B67" t="n">
-        <v>90576</v>
+        <v>74638</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7568,25 +7568,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483664</v>
+        <v>483762</v>
       </c>
       <c r="R67" t="n">
-        <v>7019708</v>
+        <v>7019692</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120420835</v>
+        <v>120420838</v>
       </c>
       <c r="B68" t="n">
-        <v>90598</v>
+        <v>74646</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7678,21 +7678,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483638</v>
+        <v>483758</v>
       </c>
       <c r="R68" t="n">
-        <v>7019659</v>
+        <v>7019694</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7768,10 +7768,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120420836</v>
+        <v>120420877</v>
       </c>
       <c r="B69" t="n">
-        <v>90598</v>
+        <v>95478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7784,21 +7784,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483663</v>
+        <v>483497</v>
       </c>
       <c r="R69" t="n">
-        <v>7019709</v>
+        <v>7019675</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120420844</v>
+        <v>120420834</v>
       </c>
       <c r="B70" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7886,25 +7886,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483852</v>
+        <v>483657</v>
       </c>
       <c r="R70" t="n">
-        <v>7019773</v>
+        <v>7019712</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120305296</v>
+        <v>120305234</v>
       </c>
       <c r="B2" t="n">
-        <v>96885</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483979</v>
+        <v>483609</v>
       </c>
       <c r="R2" t="n">
-        <v>7019514</v>
+        <v>7019727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,12 +760,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lurigt växtsätt inuti hålighet på gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305425</v>
+        <v>120305404</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483637</v>
+        <v>483788</v>
       </c>
       <c r="R3" t="n">
-        <v>7019655</v>
+        <v>7019601</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305320</v>
+        <v>120305416</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>74638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +908,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483836</v>
+        <v>483989</v>
       </c>
       <c r="R4" t="n">
-        <v>7019556</v>
+        <v>7019538</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305353</v>
+        <v>120305195</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483754</v>
+        <v>483673</v>
       </c>
       <c r="R5" t="n">
-        <v>7019590</v>
+        <v>7019675</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120305404</v>
+        <v>120305278</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483788</v>
+        <v>483813</v>
       </c>
       <c r="R7" t="n">
-        <v>7019601</v>
+        <v>7019540</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305172</v>
+        <v>120305295</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1332,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483662</v>
+        <v>483819</v>
       </c>
       <c r="R8" t="n">
-        <v>7019676</v>
+        <v>7019570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305432</v>
+        <v>120305172</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483629</v>
+        <v>483662</v>
       </c>
       <c r="R9" t="n">
-        <v>7019655</v>
+        <v>7019676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305463</v>
+        <v>120305296</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1544,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483849</v>
+        <v>483979</v>
       </c>
       <c r="R10" t="n">
-        <v>7019545</v>
+        <v>7019514</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305196</v>
+        <v>120305464</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483658</v>
+        <v>483889</v>
       </c>
       <c r="R11" t="n">
-        <v>7019677</v>
+        <v>7019544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305215</v>
+        <v>120305320</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1760,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1773,24 +1782,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483868</v>
+        <v>483836</v>
       </c>
       <c r="R12" t="n">
-        <v>7019544</v>
+        <v>7019556</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305278</v>
+        <v>120305354</v>
       </c>
       <c r="B13" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1893,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483813</v>
+        <v>483639</v>
       </c>
       <c r="R13" t="n">
-        <v>7019540</v>
+        <v>7019659</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305297</v>
+        <v>120305214</v>
       </c>
       <c r="B14" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,25 +1968,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1993,16 +1994,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484003</v>
+        <v>483756</v>
       </c>
       <c r="R14" t="n">
-        <v>7019580</v>
+        <v>7019560</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305171</v>
+        <v>120305353</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2073,25 +2082,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2105,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483590</v>
+        <v>483754</v>
       </c>
       <c r="R15" t="n">
-        <v>7019723</v>
+        <v>7019590</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305234</v>
+        <v>120305463</v>
       </c>
       <c r="B16" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,21 +2192,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2205,19 +2214,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483609</v>
+        <v>483849</v>
       </c>
       <c r="R16" t="n">
-        <v>7019727</v>
+        <v>7019545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,18 +2258,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lurigt växtsätt inuti hålighet på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2282,10 +2282,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305244</v>
+        <v>120305171</v>
       </c>
       <c r="B17" t="n">
-        <v>79527</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,25 +2294,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483828</v>
+        <v>483590</v>
       </c>
       <c r="R17" t="n">
-        <v>7019588</v>
+        <v>7019723</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120305214</v>
+        <v>120305433</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,21 +2404,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2426,24 +2426,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483756</v>
+        <v>483702</v>
       </c>
       <c r="R18" t="n">
-        <v>7019560</v>
+        <v>7019609</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305355</v>
+        <v>120305425</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2506,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2546,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483741</v>
+        <v>483637</v>
       </c>
       <c r="R19" t="n">
-        <v>7019614</v>
+        <v>7019655</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,10 +2600,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305354</v>
+        <v>120305415</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>74638</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,25 +2612,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2652,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483639</v>
+        <v>483864</v>
       </c>
       <c r="R20" t="n">
-        <v>7019659</v>
+        <v>7019545</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305464</v>
+        <v>120305213</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2722,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2758,10 +2750,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483889</v>
+        <v>483661</v>
       </c>
       <c r="R21" t="n">
-        <v>7019544</v>
+        <v>7019669</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2812,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305415</v>
+        <v>120305196</v>
       </c>
       <c r="B22" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2824,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2864,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483864</v>
+        <v>483658</v>
       </c>
       <c r="R22" t="n">
-        <v>7019545</v>
+        <v>7019677</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305295</v>
+        <v>120305215</v>
       </c>
       <c r="B23" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,25 +2930,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2964,16 +2956,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483819</v>
+        <v>483868</v>
       </c>
       <c r="R23" t="n">
-        <v>7019570</v>
+        <v>7019544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120305462</v>
+        <v>120305297</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483700</v>
+        <v>484003</v>
       </c>
       <c r="R24" t="n">
-        <v>7019608</v>
+        <v>7019580</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305416</v>
+        <v>120305355</v>
       </c>
       <c r="B25" t="n">
-        <v>74638</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483989</v>
+        <v>483741</v>
       </c>
       <c r="R25" t="n">
-        <v>7019538</v>
+        <v>7019614</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305195</v>
+        <v>120305432</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483673</v>
+        <v>483629</v>
       </c>
       <c r="R26" t="n">
-        <v>7019675</v>
+        <v>7019655</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305213</v>
+        <v>120305462</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483661</v>
+        <v>483700</v>
       </c>
       <c r="R27" t="n">
-        <v>7019669</v>
+        <v>7019608</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305433</v>
+        <v>120305244</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>79527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483702</v>
+        <v>483828</v>
       </c>
       <c r="R28" t="n">
-        <v>7019609</v>
+        <v>7019588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120382600</v>
+        <v>120383186</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,34 +3578,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483535</v>
+        <v>483495</v>
       </c>
       <c r="R29" t="n">
-        <v>7019649</v>
+        <v>7019685</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3664,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120383857</v>
+        <v>120382563</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>90576</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3680,34 +3694,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vågen, Vågen, Jmt</t>
+          <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483696</v>
+        <v>483510</v>
       </c>
       <c r="R30" t="n">
-        <v>7019783</v>
+        <v>7019662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3766,10 +3780,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120383186</v>
+        <v>120382600</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3782,48 +3796,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483495</v>
+        <v>483535</v>
       </c>
       <c r="R31" t="n">
-        <v>7019685</v>
+        <v>7019649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120382563</v>
+        <v>120383857</v>
       </c>
       <c r="B32" t="n">
-        <v>90576</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Indalsälven, Indalsälven, Jmt</t>
+          <t>Vågen, Vågen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483510</v>
+        <v>483696</v>
       </c>
       <c r="R32" t="n">
-        <v>7019662</v>
+        <v>7019783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120408137</v>
+        <v>120408144</v>
       </c>
       <c r="B34" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483624</v>
+        <v>483550</v>
       </c>
       <c r="R34" t="n">
-        <v>7019813</v>
+        <v>7019749</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4170,6 +4170,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4188,10 +4189,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120408117</v>
+        <v>120408132</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4204,21 +4205,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4229,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483561</v>
+        <v>483589</v>
       </c>
       <c r="R35" t="n">
-        <v>7019762</v>
+        <v>7019600</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4264,6 +4265,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4290,7 +4296,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120408121</v>
+        <v>120408118</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4330,10 +4336,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483627</v>
+        <v>483476</v>
       </c>
       <c r="R36" t="n">
-        <v>7019822</v>
+        <v>7019660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4370,7 +4376,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4397,10 +4403,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120408128</v>
+        <v>120408143</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4413,21 +4419,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4437,10 +4443,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483452</v>
+        <v>483743</v>
       </c>
       <c r="R37" t="n">
-        <v>7019647</v>
+        <v>7019735</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,17 +4481,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4504,10 +4506,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120408144</v>
+        <v>120408137</v>
       </c>
       <c r="B38" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4520,21 +4522,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4544,10 +4546,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483550</v>
+        <v>483624</v>
       </c>
       <c r="R38" t="n">
-        <v>7019749</v>
+        <v>7019813</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4588,7 +4590,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4607,10 +4608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120408134</v>
+        <v>120408128</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,21 +4624,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4647,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>484009</v>
+        <v>483452</v>
       </c>
       <c r="R39" t="n">
-        <v>7019590</v>
+        <v>7019647</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,6 +4684,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120408124</v>
+        <v>120408138</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,21 +4731,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4749,10 +4755,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483470</v>
+        <v>483468</v>
       </c>
       <c r="R40" t="n">
-        <v>7019656</v>
+        <v>7019617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,11 +4791,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4816,10 +4817,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120408118</v>
+        <v>120408141</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4832,21 +4833,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4856,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483476</v>
+        <v>483464</v>
       </c>
       <c r="R41" t="n">
-        <v>7019660</v>
+        <v>7019618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4892,11 +4893,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>gammalt bohål</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,10 +4919,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120408125</v>
+        <v>120408134</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4939,21 +4935,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4963,10 +4959,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483456</v>
+        <v>484009</v>
       </c>
       <c r="R42" t="n">
-        <v>7019660</v>
+        <v>7019590</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4999,11 +4995,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5030,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120408122</v>
+        <v>120408133</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5046,21 +5037,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5070,10 +5061,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483606</v>
+        <v>484009</v>
       </c>
       <c r="R43" t="n">
-        <v>7019790</v>
+        <v>7019588</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5106,11 +5097,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,7 +5123,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120408123</v>
+        <v>120408125</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5177,10 +5163,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483474</v>
+        <v>483456</v>
       </c>
       <c r="R44" t="n">
-        <v>7019669</v>
+        <v>7019660</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5217,7 +5203,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,7 +5230,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120408131</v>
+        <v>120408122</v>
       </c>
       <c r="B45" t="n">
         <v>57320</v>
@@ -5284,10 +5270,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483548</v>
+        <v>483606</v>
       </c>
       <c r="R45" t="n">
-        <v>7019602</v>
+        <v>7019790</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5351,10 +5337,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120408127</v>
+        <v>120408135</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5367,21 +5353,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5391,10 +5377,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483461</v>
+        <v>483713</v>
       </c>
       <c r="R46" t="n">
-        <v>7019658</v>
+        <v>7019760</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5427,11 +5413,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,10 +5439,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120408133</v>
+        <v>120408117</v>
       </c>
       <c r="B47" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5474,21 +5455,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5498,10 +5479,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>484009</v>
+        <v>483561</v>
       </c>
       <c r="R47" t="n">
-        <v>7019588</v>
+        <v>7019762</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5662,7 +5643,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120408132</v>
+        <v>120408124</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5702,10 +5683,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483589</v>
+        <v>483470</v>
       </c>
       <c r="R49" t="n">
-        <v>7019600</v>
+        <v>7019656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5742,7 +5723,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5769,10 +5750,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120408143</v>
+        <v>120408123</v>
       </c>
       <c r="B50" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,21 +5766,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5809,10 +5790,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483743</v>
+        <v>483474</v>
       </c>
       <c r="R50" t="n">
-        <v>7019735</v>
+        <v>7019669</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5847,13 +5828,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5872,10 +5857,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120408141</v>
+        <v>120408127</v>
       </c>
       <c r="B51" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5888,21 +5873,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5912,10 +5897,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483464</v>
+        <v>483461</v>
       </c>
       <c r="R51" t="n">
-        <v>7019618</v>
+        <v>7019658</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5948,6 +5933,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5974,10 +5964,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120408135</v>
+        <v>120408121</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5990,21 +5980,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6014,10 +6004,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483713</v>
+        <v>483627</v>
       </c>
       <c r="R52" t="n">
-        <v>7019760</v>
+        <v>7019822</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6050,6 +6040,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6076,10 +6071,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120408138</v>
+        <v>120408131</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6092,21 +6087,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483468</v>
+        <v>483548</v>
       </c>
       <c r="R53" t="n">
-        <v>7019617</v>
+        <v>7019602</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6152,6 +6147,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,10 +6178,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120420883</v>
+        <v>120420849</v>
       </c>
       <c r="B54" t="n">
-        <v>90576</v>
+        <v>79652</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483664</v>
+        <v>483572</v>
       </c>
       <c r="R54" t="n">
-        <v>7019708</v>
+        <v>7019741</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120420887</v>
+        <v>120420834</v>
       </c>
       <c r="B55" t="n">
-        <v>87423</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483979</v>
+        <v>483657</v>
       </c>
       <c r="R55" t="n">
-        <v>7019620</v>
+        <v>7019712</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120420832</v>
+        <v>120420872</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>87409</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,25 +6402,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483500</v>
+        <v>483619</v>
       </c>
       <c r="R56" t="n">
-        <v>7019677</v>
+        <v>7019709</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120420835</v>
+        <v>120420836</v>
       </c>
       <c r="B57" t="n">
         <v>90598</v>
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483638</v>
+        <v>483663</v>
       </c>
       <c r="R57" t="n">
-        <v>7019659</v>
+        <v>7019709</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6602,10 +6602,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120420830</v>
+        <v>120420837</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6618,21 +6618,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483954</v>
+        <v>483750</v>
       </c>
       <c r="R58" t="n">
-        <v>7019556</v>
+        <v>7019734</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6708,10 +6708,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120420872</v>
+        <v>120420832</v>
       </c>
       <c r="B59" t="n">
-        <v>87409</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6720,25 +6720,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483619</v>
+        <v>483500</v>
       </c>
       <c r="R59" t="n">
-        <v>7019709</v>
+        <v>7019677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6814,10 +6814,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120420844</v>
+        <v>120420838</v>
       </c>
       <c r="B60" t="n">
-        <v>96885</v>
+        <v>74646</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6826,25 +6826,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483852</v>
+        <v>483758</v>
       </c>
       <c r="R60" t="n">
-        <v>7019773</v>
+        <v>7019694</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120420833</v>
+        <v>120420887</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>87423</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483556</v>
+        <v>483979</v>
       </c>
       <c r="R61" t="n">
-        <v>7019737</v>
+        <v>7019620</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120420837</v>
+        <v>120420883</v>
       </c>
       <c r="B62" t="n">
-        <v>74646</v>
+        <v>90576</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483750</v>
+        <v>483664</v>
       </c>
       <c r="R62" t="n">
-        <v>7019734</v>
+        <v>7019708</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7132,10 +7132,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120420878</v>
+        <v>120420830</v>
       </c>
       <c r="B63" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7148,21 +7148,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483767</v>
+        <v>483954</v>
       </c>
       <c r="R63" t="n">
-        <v>7019702</v>
+        <v>7019556</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120420831</v>
+        <v>120420877</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483607</v>
+        <v>483497</v>
       </c>
       <c r="R64" t="n">
-        <v>7019631</v>
+        <v>7019675</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120420836</v>
+        <v>120420831</v>
       </c>
       <c r="B65" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483663</v>
+        <v>483607</v>
       </c>
       <c r="R65" t="n">
-        <v>7019709</v>
+        <v>7019631</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7450,10 +7450,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120420849</v>
+        <v>120420844</v>
       </c>
       <c r="B66" t="n">
-        <v>79652</v>
+        <v>96885</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7466,21 +7466,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483572</v>
+        <v>483852</v>
       </c>
       <c r="R66" t="n">
-        <v>7019741</v>
+        <v>7019773</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120420838</v>
+        <v>120420878</v>
       </c>
       <c r="B68" t="n">
-        <v>74646</v>
+        <v>95478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7678,21 +7678,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483758</v>
+        <v>483767</v>
       </c>
       <c r="R68" t="n">
-        <v>7019694</v>
+        <v>7019702</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7768,10 +7768,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120420877</v>
+        <v>120420833</v>
       </c>
       <c r="B69" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7784,21 +7784,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483497</v>
+        <v>483556</v>
       </c>
       <c r="R69" t="n">
-        <v>7019675</v>
+        <v>7019737</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120420834</v>
+        <v>120420835</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7890,21 +7890,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483657</v>
+        <v>483638</v>
       </c>
       <c r="R70" t="n">
-        <v>7019712</v>
+        <v>7019659</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 1955-2022 artfynd.xlsx
+++ b/artfynd/A 1955-2022 artfynd.xlsx
@@ -3562,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120383186</v>
+        <v>120382563</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,48 +3578,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483495</v>
+        <v>483510</v>
       </c>
       <c r="R29" t="n">
-        <v>7019685</v>
+        <v>7019662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,10 +3664,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120382563</v>
+        <v>120383186</v>
       </c>
       <c r="B30" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3694,34 +3680,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Indalsälven, Indalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483510</v>
+        <v>483495</v>
       </c>
       <c r="R30" t="n">
-        <v>7019662</v>
+        <v>7019685</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
